--- a/apps/deep/www/calculators/southeastern-plains.xlsx
+++ b/apps/deep/www/calculators/southeastern-plains.xlsx
@@ -16,72 +16,74 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChartData" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="curve_key">'Reference'!$A$5:$A$32</definedName>
-    <definedName name="curve_x1">'Reference'!$G$5:$G$32</definedName>
-    <definedName name="curve_y1">'Reference'!$O$5:$O$32</definedName>
-    <definedName name="curve_x2">'Reference'!$H$5:$H$32</definedName>
-    <definedName name="curve_y2">'Reference'!$P$5:$P$32</definedName>
-    <definedName name="curve_x3">'Reference'!$I$5:$I$32</definedName>
-    <definedName name="curve_y3">'Reference'!$Q$5:$Q$32</definedName>
-    <definedName name="curve_x4">'Reference'!$J$5:$J$32</definedName>
-    <definedName name="curve_y4">'Reference'!$R$5:$R$32</definedName>
-    <definedName name="curve_x5">'Reference'!$K$5:$K$32</definedName>
-    <definedName name="curve_y5">'Reference'!$S$5:$S$32</definedName>
-    <definedName name="curve_x6">'Reference'!$L$5:$L$32</definedName>
-    <definedName name="curve_y6">'Reference'!$T$5:$T$32</definedName>
-    <definedName name="curve_x7">'Reference'!$M$5:$M$32</definedName>
-    <definedName name="curve_y7">'Reference'!$U$5:$U$32</definedName>
-    <definedName name="curve_x8">'Reference'!$N$5:$N$32</definedName>
-    <definedName name="curve_y8">'Reference'!$V$5:$V$32</definedName>
-    <definedName name="strata_spring_phab_lrbs_use">'Reference'!$A$36:$A$39</definedName>
+    <definedName name="curve_key">'Reference'!$A$5:$A$33</definedName>
+    <definedName name="curve_x1">'Reference'!$G$5:$G$33</definedName>
+    <definedName name="curve_y1">'Reference'!$O$5:$O$33</definedName>
+    <definedName name="curve_x2">'Reference'!$H$5:$H$33</definedName>
+    <definedName name="curve_y2">'Reference'!$P$5:$P$33</definedName>
+    <definedName name="curve_x3">'Reference'!$I$5:$I$33</definedName>
+    <definedName name="curve_y3">'Reference'!$Q$5:$Q$33</definedName>
+    <definedName name="curve_x4">'Reference'!$J$5:$J$33</definedName>
+    <definedName name="curve_y4">'Reference'!$R$5:$R$33</definedName>
+    <definedName name="curve_x5">'Reference'!$K$5:$K$33</definedName>
+    <definedName name="curve_y5">'Reference'!$S$5:$S$33</definedName>
+    <definedName name="curve_x6">'Reference'!$L$5:$L$33</definedName>
+    <definedName name="curve_y6">'Reference'!$T$5:$T$33</definedName>
+    <definedName name="curve_x7">'Reference'!$M$5:$M$33</definedName>
+    <definedName name="curve_y7">'Reference'!$U$5:$U$33</definedName>
+    <definedName name="curve_x8">'Reference'!$N$5:$N$33</definedName>
+    <definedName name="curve_y8">'Reference'!$V$5:$V$33</definedName>
+    <definedName name="strata_spring_phab_lrbs_use">'Reference'!$A$37:$A$40</definedName>
     <definedName name="idx_spring_pctimp2019ws">'Metrics'!$V$5</definedName>
     <definedName name="idx_spring_pctag2019ws">'Metrics'!$V$6</definedName>
-    <definedName name="idx_spring_rddensws">'Metrics'!$V$7</definedName>
-    <definedName name="idx_spring_bfiws">'Metrics'!$V$8</definedName>
-    <definedName name="idx_spring_dorws">'Metrics'!$V$9</definedName>
-    <definedName name="idx_spring_phab_bfwd_rat">'Metrics'!$V$10</definedName>
-    <definedName name="idx_spring_phab_pct_safn">'Metrics'!$V$11</definedName>
-    <definedName name="idx_spring_phab_xembed">'Metrics'!$V$12</definedName>
-    <definedName name="idx_spring_phab_sinu">'Metrics'!$V$13</definedName>
-    <definedName name="idx_spring_phab_xbka">'Metrics'!$V$14</definedName>
-    <definedName name="idx_spring_phab_lrbs_use">'Metrics'!$V$15</definedName>
-    <definedName name="idx_spring_phab_lwdeqvolm100">'Metrics'!$V$16</definedName>
-    <definedName name="idx_spring_phab_xcdenmid">'Metrics'!$V$17</definedName>
-    <definedName name="idx_spring_phab_xcmgw">'Metrics'!$V$18</definedName>
-    <definedName name="idx_spring_chem_ntl">'Metrics'!$V$19</definedName>
-    <definedName name="idx_spring_chem_ptl">'Metrics'!$V$20</definedName>
-    <definedName name="idx_spring_chem_ph">'Metrics'!$V$21</definedName>
-    <definedName name="idx_spring_chem_turb">'Metrics'!$V$22</definedName>
-    <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$23</definedName>
-    <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$24</definedName>
-    <definedName name="idx_spring_bent_totlntax">'Metrics'!$V$25</definedName>
-    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$26</definedName>
-    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$27</definedName>
-    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$28</definedName>
-    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$29</definedName>
+    <definedName name="idx_spring_pctwet2019ws">'Metrics'!$V$7</definedName>
+    <definedName name="idx_spring_rddensws">'Metrics'!$V$8</definedName>
+    <definedName name="idx_spring_bfiws">'Metrics'!$V$9</definedName>
+    <definedName name="idx_spring_dorws">'Metrics'!$V$10</definedName>
+    <definedName name="idx_spring_phab_bfwd_rat">'Metrics'!$V$11</definedName>
+    <definedName name="idx_spring_phab_pct_safn">'Metrics'!$V$12</definedName>
+    <definedName name="idx_spring_phab_xembed">'Metrics'!$V$13</definedName>
+    <definedName name="idx_spring_phab_sinu">'Metrics'!$V$14</definedName>
+    <definedName name="idx_spring_phab_xbka">'Metrics'!$V$15</definedName>
+    <definedName name="idx_spring_phab_lrbs_use">'Metrics'!$V$16</definedName>
+    <definedName name="idx_spring_phab_lwdeqvolm100">'Metrics'!$V$17</definedName>
+    <definedName name="idx_spring_phab_xcdenmid">'Metrics'!$V$18</definedName>
+    <definedName name="idx_spring_phab_xcmgw">'Metrics'!$V$19</definedName>
+    <definedName name="idx_spring_chem_ntl">'Metrics'!$V$20</definedName>
+    <definedName name="idx_spring_chem_ptl">'Metrics'!$V$21</definedName>
+    <definedName name="idx_spring_chem_ph">'Metrics'!$V$22</definedName>
+    <definedName name="idx_spring_chem_turb">'Metrics'!$V$23</definedName>
+    <definedName name="idx_spring_phab_pct_fast">'Metrics'!$V$24</definedName>
+    <definedName name="idx_spring_phab_xfc_nat">'Metrics'!$V$25</definedName>
+    <definedName name="idx_spring_bent_totlntax">'Metrics'!$V$26</definedName>
+    <definedName name="idx_spring_fish_nat_totlntax">'Metrics'!$V$27</definedName>
+    <definedName name="idx_spring_bent_ept_ntax">'Metrics'!$V$28</definedName>
+    <definedName name="idx_spring_bent_hprime">'Metrics'!$V$29</definedName>
+    <definedName name="idx_spring_nid_dams_1mi">'Metrics'!$V$30</definedName>
     <definedName name="fs_catchment_hydrology">'Results'!$B$4</definedName>
-    <definedName name="fs_reach_inflow">'Results'!$B$5</definedName>
-    <definedName name="fs_streamflow_regime">'Results'!$B$6</definedName>
-    <definedName name="fs_low_flow_baseflow_dynamics">'Results'!$B$7</definedName>
-    <definedName name="fs_high_flow_dynamics">'Results'!$B$8</definedName>
-    <definedName name="fs_floodplain_connectivity">'Results'!$B$9</definedName>
-    <definedName name="fs_hyporheic_connectivity">'Results'!$B$10</definedName>
-    <definedName name="fs_channel_evolution">'Results'!$B$11</definedName>
-    <definedName name="fs_channel_floodplain_dynamics">'Results'!$B$12</definedName>
-    <definedName name="fs_sediment_continuity">'Results'!$B$13</definedName>
-    <definedName name="fs_bed_composition_bedform_dynamics">'Results'!$B$14</definedName>
-    <definedName name="fs_light_thermal_regime">'Results'!$B$15</definedName>
-    <definedName name="fs_carbon_processing">'Results'!$B$16</definedName>
-    <definedName name="fs_nutrient_cycling">'Results'!$B$17</definedName>
-    <definedName name="fs_water_soil_quality">'Results'!$B$18</definedName>
-    <definedName name="fs_habitat_provision">'Results'!$B$19</definedName>
-    <definedName name="fs_population_support">'Results'!$B$20</definedName>
-    <definedName name="fs_community_dynamics">'Results'!$B$21</definedName>
-    <definedName name="fs_watershed_connectivity">'Results'!$B$22</definedName>
-    <definedName name="sub_index_physical">'Results'!$B$25</definedName>
-    <definedName name="sub_index_chemical">'Results'!$B$26</definedName>
-    <definedName name="sub_index_biological">'Results'!$B$27</definedName>
-    <definedName name="eci">'Results'!$B$28</definedName>
+    <definedName name="fs_surface_water_storage">'Results'!$B$5</definedName>
+    <definedName name="fs_reach_inflow">'Results'!$B$6</definedName>
+    <definedName name="fs_streamflow_regime">'Results'!$B$7</definedName>
+    <definedName name="fs_low_flow_baseflow_dynamics">'Results'!$B$8</definedName>
+    <definedName name="fs_high_flow_dynamics">'Results'!$B$9</definedName>
+    <definedName name="fs_floodplain_connectivity">'Results'!$B$10</definedName>
+    <definedName name="fs_hyporheic_connectivity">'Results'!$B$11</definedName>
+    <definedName name="fs_channel_evolution">'Results'!$B$12</definedName>
+    <definedName name="fs_channel_floodplain_dynamics">'Results'!$B$13</definedName>
+    <definedName name="fs_sediment_continuity">'Results'!$B$14</definedName>
+    <definedName name="fs_bed_composition_bedform_dynamics">'Results'!$B$15</definedName>
+    <definedName name="fs_light_thermal_regime">'Results'!$B$16</definedName>
+    <definedName name="fs_carbon_processing">'Results'!$B$17</definedName>
+    <definedName name="fs_nutrient_cycling">'Results'!$B$18</definedName>
+    <definedName name="fs_water_soil_quality">'Results'!$B$19</definedName>
+    <definedName name="fs_habitat_provision">'Results'!$B$20</definedName>
+    <definedName name="fs_population_support">'Results'!$B$21</definedName>
+    <definedName name="fs_community_dynamics">'Results'!$B$22</definedName>
+    <definedName name="fs_watershed_connectivity">'Results'!$B$23</definedName>
+    <definedName name="sub_index_physical">'Results'!$B$26</definedName>
+    <definedName name="sub_index_chemical">'Results'!$B$27</definedName>
+    <definedName name="sub_index_biological">'Results'!$B$28</definedName>
+    <definedName name="eci">'Results'!$B$29</definedName>
     <definedName name="site_name">'DEEP Score'!$B$5</definedName>
     <definedName name="site_reach">'DEEP Score'!$B$6</definedName>
     <definedName name="site_coords">'DEEP Score'!$B$7</definedName>
@@ -89,31 +91,32 @@
     <definedName name="site_assessor">'DEEP Score'!$B$9</definedName>
     <definedName name="in_spring_pctimp2019ws">'DEEP Score'!$E$12</definedName>
     <definedName name="in_spring_pctag2019ws">'DEEP Score'!$E$13</definedName>
-    <definedName name="in_spring_rddensws">'DEEP Score'!$E$14</definedName>
-    <definedName name="in_spring_bfiws">'DEEP Score'!$E$15</definedName>
-    <definedName name="in_spring_dorws">'DEEP Score'!$E$16</definedName>
-    <definedName name="in_spring_phab_bfwd_rat">'DEEP Score'!$E$18</definedName>
-    <definedName name="in_spring_phab_pct_safn">'DEEP Score'!$E$21</definedName>
-    <definedName name="in_spring_phab_xembed">'DEEP Score'!$E$22</definedName>
-    <definedName name="in_spring_phab_sinu">'DEEP Score'!$E$24</definedName>
-    <definedName name="in_spring_phab_xbka">'DEEP Score'!$E$25</definedName>
-    <definedName name="in_spring_phab_lrbs_use">'DEEP Score'!$E$26</definedName>
-    <definedName name="st_spring_phab_lrbs_use">'DEEP Score'!$F$26</definedName>
-    <definedName name="in_spring_phab_lwdeqvolm100">'DEEP Score'!$E$28</definedName>
-    <definedName name="in_spring_phab_xcdenmid">'DEEP Score'!$E$30</definedName>
-    <definedName name="in_spring_phab_xcmgw">'DEEP Score'!$E$31</definedName>
-    <definedName name="in_spring_chem_ntl">'DEEP Score'!$E$32</definedName>
-    <definedName name="in_spring_chem_ptl">'DEEP Score'!$E$33</definedName>
-    <definedName name="in_spring_chem_ph">'DEEP Score'!$E$34</definedName>
-    <definedName name="in_spring_chem_turb">'DEEP Score'!$E$35</definedName>
-    <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$36</definedName>
-    <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$37</definedName>
-    <definedName name="in_spring_bent_totlntax">'DEEP Score'!$E$38</definedName>
-    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$39</definedName>
-    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$40</definedName>
-    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$41</definedName>
-    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$42</definedName>
-    <definedName name="site_notes">'DEEP Score'!$A$63</definedName>
+    <definedName name="in_spring_pctwet2019ws">'DEEP Score'!$E$14</definedName>
+    <definedName name="in_spring_rddensws">'DEEP Score'!$E$15</definedName>
+    <definedName name="in_spring_bfiws">'DEEP Score'!$E$16</definedName>
+    <definedName name="in_spring_dorws">'DEEP Score'!$E$17</definedName>
+    <definedName name="in_spring_phab_bfwd_rat">'DEEP Score'!$E$19</definedName>
+    <definedName name="in_spring_phab_pct_safn">'DEEP Score'!$E$22</definedName>
+    <definedName name="in_spring_phab_xembed">'DEEP Score'!$E$23</definedName>
+    <definedName name="in_spring_phab_sinu">'DEEP Score'!$E$25</definedName>
+    <definedName name="in_spring_phab_xbka">'DEEP Score'!$E$26</definedName>
+    <definedName name="in_spring_phab_lrbs_use">'DEEP Score'!$E$27</definedName>
+    <definedName name="st_spring_phab_lrbs_use">'DEEP Score'!$F$27</definedName>
+    <definedName name="in_spring_phab_lwdeqvolm100">'DEEP Score'!$E$29</definedName>
+    <definedName name="in_spring_phab_xcdenmid">'DEEP Score'!$E$31</definedName>
+    <definedName name="in_spring_phab_xcmgw">'DEEP Score'!$E$32</definedName>
+    <definedName name="in_spring_chem_ntl">'DEEP Score'!$E$33</definedName>
+    <definedName name="in_spring_chem_ptl">'DEEP Score'!$E$34</definedName>
+    <definedName name="in_spring_chem_ph">'DEEP Score'!$E$35</definedName>
+    <definedName name="in_spring_chem_turb">'DEEP Score'!$E$36</definedName>
+    <definedName name="in_spring_phab_pct_fast">'DEEP Score'!$E$37</definedName>
+    <definedName name="in_spring_phab_xfc_nat">'DEEP Score'!$E$38</definedName>
+    <definedName name="in_spring_bent_totlntax">'DEEP Score'!$E$39</definedName>
+    <definedName name="in_spring_fish_nat_totlntax">'DEEP Score'!$E$40</definedName>
+    <definedName name="in_spring_bent_ept_ntax">'DEEP Score'!$E$41</definedName>
+    <definedName name="in_spring_bent_hprime">'DEEP Score'!$E$42</definedName>
+    <definedName name="in_spring_nid_dams_1mi">'DEEP Score'!$E$43</definedName>
+    <definedName name="site_notes">'DEEP Score'!$A$62</definedName>
     <definedName name="meta_assessment_id">'Metadata'!$B$4</definedName>
     <definedName name="meta_assessment_name">'Metadata'!$B$5</definedName>
     <definedName name="meta_version">'Metadata'!$B$6</definedName>
@@ -828,12 +831,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$3:$A$21</f>
+              <f>'ChartData'!$A$3:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$C$3:$C$21</f>
+              <f>'ChartData'!$C$3:$C$22</f>
             </numRef>
           </val>
         </ser>
@@ -858,12 +861,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$3:$A$21</f>
+              <f>'ChartData'!$A$3:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$D$3:$D$21</f>
+              <f>'ChartData'!$D$3:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -888,12 +891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$3:$A$21</f>
+              <f>'ChartData'!$A$3:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$E$3:$E$21</f>
+              <f>'ChartData'!$E$3:$E$22</f>
             </numRef>
           </val>
         </ser>
@@ -982,7 +985,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'ChartData'!C23</f>
+              <f>'ChartData'!C24</f>
             </strRef>
           </tx>
           <spPr>
@@ -998,12 +1001,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$24:$A$26</f>
+              <f>'ChartData'!$A$25:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$C$24:$C$26</f>
+              <f>'ChartData'!$C$25:$C$27</f>
             </numRef>
           </val>
         </ser>
@@ -1012,7 +1015,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'ChartData'!D23</f>
+              <f>'ChartData'!D24</f>
             </strRef>
           </tx>
           <spPr>
@@ -1028,12 +1031,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$24:$A$26</f>
+              <f>'ChartData'!$A$25:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$D$24:$D$26</f>
+              <f>'ChartData'!$D$25:$D$27</f>
             </numRef>
           </val>
         </ser>
@@ -1042,7 +1045,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'ChartData'!E23</f>
+              <f>'ChartData'!E24</f>
             </strRef>
           </tx>
           <spPr>
@@ -1058,12 +1061,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'ChartData'!$A$24:$A$26</f>
+              <f>'ChartData'!$A$25:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ChartData'!$E$24:$E$26</f>
+              <f>'ChartData'!$E$25:$E$27</f>
             </numRef>
           </val>
         </ser>
@@ -1132,7 +1135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="4240800"/>
+    <ext cx="7920000" cy="4464000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1151,7 +1154,7 @@
     <from>
       <col>10</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="2340000"/>
@@ -1488,10 +1491,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 18 curves are fitted to least-disturbed stations of this ecoregion. 4 curves are fitted to this ecoregion's own streams under the documented regional screen, which relaxes agriculture only. 3 borrow comparable least-disturbed stations from a wider region, stating the region and the transfer risk. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
+          <t>Reference condition. Reference condition is set by a fixed landscape-pressure screen, never by a score. 18 curves are fitted to least-disturbed stations of this ecoregion. 4 curves are fitted to this ecoregion's own streams under the documented regional screen, which relaxes agriculture only. 3 borrow comparable least-disturbed stations from a wider region, stating the region and the transfer risk. 20 of these curves carried forward unchanged from version 1. A metric that no basis supports is not scored, and the function it would have scored is reported as unassessed.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1601,7 +1604,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Version 1 | USEPA NRSA 2013-24 (L3 ecoregion 65), StreamCurves regional analysis, methodology 0.14-provisional</t>
+          <t>Version 2 | USEPA NRSA 2013-24 (L3 ecoregion 65), StreamCurves regional analysis, methodology 0.14-provisional</t>
         </is>
       </c>
     </row>
@@ -1768,17 +1771,17 @@
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
-          <t>Reach inflow</t>
+          <t>Surface water storage</t>
         </is>
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
-          <t>Road density</t>
+          <t>Wetland</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>km/sq km</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E14" s="31" t="n"/>
@@ -1797,158 +1800,155 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Hydrology</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Reach inflow</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Road density</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>km/sq km</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="32" t="inlineStr"/>
+      <c r="G15" s="33">
+        <f>IF('Metrics'!$V$8="","",'Metrics'!$V$8)</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF('Results'!$B$6="","",'Results'!$B$6)</f>
+        <v/>
+      </c>
+      <c r="I15" s="35">
+        <f>IF('DEEP Score'!$H$15="","",IF('DEEP Score'!$H$15&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$15&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Hydrology</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Streamflow regime</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Base flow index</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="15" t="inlineStr"/>
-      <c r="G15" s="16">
-        <f>IF('Metrics'!$V$8="","",'Metrics'!$V$8)</f>
-        <v/>
-      </c>
-      <c r="H15" s="17">
-        <f>IF('Results'!$B$6="","",'Results'!$B$6)</f>
-        <v/>
-      </c>
-      <c r="I15" s="18">
-        <f>IF('DEEP Score'!$H$15="","",IF('DEEP Score'!$H$15&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$15&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="n"/>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="15" t="inlineStr"/>
+      <c r="G16" s="16">
+        <f>IF('Metrics'!$V$9="","",'Metrics'!$V$9)</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>IF('Results'!$B$7="","",'Results'!$B$7)</f>
+        <v/>
+      </c>
+      <c r="I16" s="18">
+        <f>IF('DEEP Score'!$H$16="","",IF('DEEP Score'!$H$16&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$16&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>Degree of regulation</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="24" t="inlineStr"/>
-      <c r="G16" s="25">
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="24" t="inlineStr"/>
+      <c r="G17" s="25">
+        <f>IF('Metrics'!$V$10="","",'Metrics'!$V$10)</f>
+        <v/>
+      </c>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="26" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
+        <is>
+          <t>Hydraulics</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Low flow and baseflow dynamics</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Base flow index</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E18" s="37">
+        <f>IF('DEEP Score'!$E$16="","",'DEEP Score'!$E$16)</f>
+        <v/>
+      </c>
+      <c r="F18" s="38" t="inlineStr"/>
+      <c r="G18" s="16">
         <f>IF('Metrics'!$V$9="","",'Metrics'!$V$9)</f>
         <v/>
       </c>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="26" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="inlineStr">
-        <is>
-          <t>Hydraulics</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Low flow and baseflow dynamics</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Base flow index</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E17" s="37">
-        <f>IF('DEEP Score'!$E$15="","",'DEEP Score'!$E$15)</f>
-        <v/>
-      </c>
-      <c r="F17" s="38" t="inlineStr"/>
-      <c r="G17" s="16">
-        <f>IF('Metrics'!$V$8="","",'Metrics'!$V$8)</f>
-        <v/>
-      </c>
-      <c r="H17" s="17">
-        <f>IF('Results'!$B$7="","",'Results'!$B$7)</f>
-        <v/>
-      </c>
-      <c r="I17" s="18">
-        <f>IF('DEEP Score'!$H$17="","",IF('DEEP Score'!$H$17&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$17&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="n"/>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="H18" s="17">
+        <f>IF('Results'!$B$8="","",'Results'!$B$8)</f>
+        <v/>
+      </c>
+      <c r="I18" s="18">
+        <f>IF('DEEP Score'!$H$18="","",IF('DEEP Score'!$H$18&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$18&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>Bankfull width:depth ratio</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="24" t="inlineStr"/>
-      <c r="G18" s="25">
-        <f>IF('Metrics'!$V$10="","",'Metrics'!$V$10)</f>
-        <v/>
-      </c>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="26" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>Hydraulics</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>High flow dynamics</t>
-        </is>
-      </c>
-      <c r="C19" s="29" t="inlineStr">
-        <is>
-          <t>Impervious surface</t>
-        </is>
-      </c>
-      <c r="D19" s="30" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E19" s="40">
-        <f>IF('DEEP Score'!$E$12="","",'DEEP Score'!$E$12)</f>
-        <v/>
-      </c>
-      <c r="F19" s="41" t="inlineStr"/>
-      <c r="G19" s="33">
-        <f>IF('Metrics'!$V$5="","",'Metrics'!$V$5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="34">
-        <f>IF('Results'!$B$8="","",'Results'!$B$8)</f>
-        <v/>
-      </c>
-      <c r="I19" s="35">
-        <f>IF('DEEP Score'!$H$19="","",IF('DEEP Score'!$H$19&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$19&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
+      <c r="D19" s="22" t="inlineStr"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="24" t="inlineStr"/>
+      <c r="G19" s="25">
+        <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
+        <v/>
+      </c>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="26" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="39" t="inlineStr">
@@ -1958,22 +1958,26 @@
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>Floodplain connectivity</t>
+          <t>High flow dynamics</t>
         </is>
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>Bankfull width:depth ratio</t>
-        </is>
-      </c>
-      <c r="D20" s="30" t="inlineStr"/>
+          <t>Impervious surface</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="E20" s="40">
-        <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
+        <f>IF('DEEP Score'!$E$12="","",'DEEP Score'!$E$12)</f>
         <v/>
       </c>
       <c r="F20" s="41" t="inlineStr"/>
       <c r="G20" s="33">
-        <f>IF('Metrics'!$V$10="","",'Metrics'!$V$10)</f>
+        <f>IF('Metrics'!$V$5="","",'Metrics'!$V$5)</f>
         <v/>
       </c>
       <c r="H20" s="34">
@@ -1986,313 +1990,312 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Hydraulics</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Floodplain connectivity</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>Bankfull width:depth ratio</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr"/>
+      <c r="E21" s="40">
+        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
+        <v/>
+      </c>
+      <c r="F21" s="41" t="inlineStr"/>
+      <c r="G21" s="33">
+        <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF('Results'!$B$10="","",'Results'!$B$10)</f>
+        <v/>
+      </c>
+      <c r="I21" s="35">
+        <f>IF('DEEP Score'!$H$21="","",IF('DEEP Score'!$H$21&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$21&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>Hydraulics</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Hyporheic connectivity</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Sand + fines</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="15" t="inlineStr"/>
-      <c r="G21" s="16">
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="16">
+        <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
+        <v/>
+      </c>
+      <c r="H22" s="17">
+        <f>IF('Results'!$B$11="","",'Results'!$B$11)</f>
+        <v/>
+      </c>
+      <c r="I22" s="18">
+        <f>IF('DEEP Score'!$H$22="","",IF('DEEP Score'!$H$22&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$22&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Embeddedness</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="24" t="inlineStr"/>
+      <c r="G23" s="25">
+        <f>IF('Metrics'!$V$13="","",'Metrics'!$V$13)</f>
+        <v/>
+      </c>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="26" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Geomorphology</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>Channel evolution</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>Bankfull width:depth ratio</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr"/>
+      <c r="E24" s="40">
+        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
+        <v/>
+      </c>
+      <c r="F24" s="41" t="inlineStr"/>
+      <c r="G24" s="33">
         <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
         <v/>
       </c>
-      <c r="H21" s="17">
-        <f>IF('Results'!$B$10="","",'Results'!$B$10)</f>
-        <v/>
-      </c>
-      <c r="I21" s="18">
-        <f>IF('DEEP Score'!$H$21="","",IF('DEEP Score'!$H$21&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$21&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="H24" s="34">
+        <f>IF('Results'!$B$12="","",'Results'!$B$12)</f>
+        <v/>
+      </c>
+      <c r="I24" s="35">
+        <f>IF('DEEP Score'!$H$24="","",IF('DEEP Score'!$H$24&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$24&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>Geomorphology</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Channel and floodplain dynamics</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Sinuosity</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="15" t="inlineStr"/>
+      <c r="G25" s="16">
+        <f>IF('Metrics'!$V$14="","",'Metrics'!$V$14)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>IF('Results'!$B$13="","",'Results'!$B$13)</f>
+        <v/>
+      </c>
+      <c r="I25" s="18">
+        <f>IF('DEEP Score'!$H$25="","",IF('DEEP Score'!$H$25&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$25&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Bank angle</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>degrees</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="24" t="inlineStr"/>
+      <c r="G26" s="25">
+        <f>IF('Metrics'!$V$15="","",'Metrics'!$V$15)</f>
+        <v/>
+      </c>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="26" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>Geomorphology</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Sediment continuity</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Relative bed stability</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>log</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>All streams (pooled)</t>
+        </is>
+      </c>
+      <c r="G27" s="16">
+        <f>IF('Metrics'!$V$16="","",'Metrics'!$V$16)</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>IF('Results'!$B$14="","",'Results'!$B$14)</f>
+        <v/>
+      </c>
+      <c r="I27" s="18">
+        <f>IF('DEEP Score'!$H$27="","",IF('DEEP Score'!$H$27&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$27&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="n"/>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Sand + fines</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E28" s="45">
+        <f>IF('DEEP Score'!$E$22="","",'DEEP Score'!$E$22)</f>
+        <v/>
+      </c>
+      <c r="F28" s="46" t="inlineStr"/>
+      <c r="G28" s="25">
+        <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
+        <v/>
+      </c>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
+        <is>
+          <t>Geomorphology</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Bed composition and bedform dynamics</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Large wood volume</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>m3/100m</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="15" t="inlineStr"/>
+      <c r="G29" s="16">
+        <f>IF('Metrics'!$V$17="","",'Metrics'!$V$17)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>IF('Results'!$B$15="","",'Results'!$B$15)</f>
+        <v/>
+      </c>
+      <c r="I29" s="18">
+        <f>IF('DEEP Score'!$H$29="","",IF('DEEP Score'!$H$29&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$29&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>Embeddedness</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="24" t="inlineStr"/>
-      <c r="G22" s="25">
-        <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
-        <v/>
-      </c>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="26" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="42" t="inlineStr">
-        <is>
-          <t>Geomorphology</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>Channel evolution</t>
-        </is>
-      </c>
-      <c r="C23" s="29" t="inlineStr">
-        <is>
-          <t>Bankfull width:depth ratio</t>
-        </is>
-      </c>
-      <c r="D23" s="30" t="inlineStr"/>
-      <c r="E23" s="40">
-        <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
-        <v/>
-      </c>
-      <c r="F23" s="41" t="inlineStr"/>
-      <c r="G23" s="33">
-        <f>IF('Metrics'!$V$10="","",'Metrics'!$V$10)</f>
-        <v/>
-      </c>
-      <c r="H23" s="34">
-        <f>IF('Results'!$B$11="","",'Results'!$B$11)</f>
-        <v/>
-      </c>
-      <c r="I23" s="35">
-        <f>IF('DEEP Score'!$H$23="","",IF('DEEP Score'!$H$23&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$23&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>Geomorphology</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Channel and floodplain dynamics</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Sinuosity</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="15" t="inlineStr"/>
-      <c r="G24" s="16">
+      <c r="E30" s="45">
+        <f>IF('DEEP Score'!$E$23="","",'DEEP Score'!$E$23)</f>
+        <v/>
+      </c>
+      <c r="F30" s="46" t="inlineStr"/>
+      <c r="G30" s="25">
         <f>IF('Metrics'!$V$13="","",'Metrics'!$V$13)</f>
         <v/>
       </c>
-      <c r="H24" s="17">
-        <f>IF('Results'!$B$12="","",'Results'!$B$12)</f>
-        <v/>
-      </c>
-      <c r="I24" s="18">
-        <f>IF('DEEP Score'!$H$24="","",IF('DEEP Score'!$H$24&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$24&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="n"/>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>Bank angle</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>degrees</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="24" t="inlineStr"/>
-      <c r="G25" s="25">
-        <f>IF('Metrics'!$V$14="","",'Metrics'!$V$14)</f>
-        <v/>
-      </c>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="26" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>Geomorphology</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Sediment continuity</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Relative bed stability</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>log</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="44" t="inlineStr">
-        <is>
-          <t>All streams (pooled)</t>
-        </is>
-      </c>
-      <c r="G26" s="16">
-        <f>IF('Metrics'!$V$15="","",'Metrics'!$V$15)</f>
-        <v/>
-      </c>
-      <c r="H26" s="17">
-        <f>IF('Results'!$B$13="","",'Results'!$B$13)</f>
-        <v/>
-      </c>
-      <c r="I26" s="18">
-        <f>IF('DEEP Score'!$H$26="","",IF('DEEP Score'!$H$26&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$26&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>Sand + fines</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E27" s="45">
-        <f>IF('DEEP Score'!$E$21="","",'DEEP Score'!$E$21)</f>
-        <v/>
-      </c>
-      <c r="F27" s="46" t="inlineStr"/>
-      <c r="G27" s="25">
-        <f>IF('Metrics'!$V$11="","",'Metrics'!$V$11)</f>
-        <v/>
-      </c>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="26" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>Geomorphology</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Bed composition and bedform dynamics</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>Large wood volume</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>m3/100m</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="15" t="inlineStr"/>
-      <c r="G28" s="16">
-        <f>IF('Metrics'!$V$16="","",'Metrics'!$V$16)</f>
-        <v/>
-      </c>
-      <c r="H28" s="17">
-        <f>IF('Results'!$B$14="","",'Results'!$B$14)</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>IF('DEEP Score'!$H$28="","",IF('DEEP Score'!$H$28&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$28&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>Embeddedness</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E29" s="45">
-        <f>IF('DEEP Score'!$E$22="","",'DEEP Score'!$E$22)</f>
-        <v/>
-      </c>
-      <c r="F29" s="46" t="inlineStr"/>
-      <c r="G29" s="25">
-        <f>IF('Metrics'!$V$12="","",'Metrics'!$V$12)</f>
-        <v/>
-      </c>
-      <c r="H29" s="20" t="n"/>
-      <c r="I29" s="26" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="47" t="inlineStr">
-        <is>
-          <t>Physicochemistry</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>Light &amp; thermal regime</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="inlineStr">
-        <is>
-          <t>Canopy density, mid-channel</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="32" t="inlineStr"/>
-      <c r="G30" s="33">
-        <f>IF('Metrics'!$V$17="","",'Metrics'!$V$17)</f>
-        <v/>
-      </c>
-      <c r="H30" s="34">
-        <f>IF('Results'!$B$15="","",'Results'!$B$15)</f>
-        <v/>
-      </c>
-      <c r="I30" s="35">
-        <f>IF('DEEP Score'!$H$30="","",IF('DEEP Score'!$H$30&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$30&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="47" t="inlineStr">
@@ -2302,17 +2305,17 @@
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>Carbon processing</t>
+          <t>Light &amp; thermal regime</t>
         </is>
       </c>
       <c r="C31" s="29" t="inlineStr">
         <is>
-          <t>Riparian veg cover, woody</t>
+          <t>Canopy density, mid-channel</t>
         </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>frac</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E31" s="31" t="n"/>
@@ -2331,362 +2334,383 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="48" t="inlineStr">
+      <c r="A32" s="47" t="inlineStr">
         <is>
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
+        <is>
+          <t>Carbon processing</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>Riparian veg cover, woody</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="32" t="inlineStr"/>
+      <c r="G32" s="33">
+        <f>IF('Metrics'!$V$19="","",'Metrics'!$V$19)</f>
+        <v/>
+      </c>
+      <c r="H32" s="34">
+        <f>IF('Results'!$B$17="","",'Results'!$B$17)</f>
+        <v/>
+      </c>
+      <c r="I32" s="35">
+        <f>IF('DEEP Score'!$H$32="","",IF('DEEP Score'!$H$32&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$32&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>Physicochemistry</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Nutrient cycling</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Total nitrogen</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>mg N/L</t>
         </is>
       </c>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="15" t="inlineStr"/>
-      <c r="G32" s="16">
-        <f>IF('Metrics'!$V$19="","",'Metrics'!$V$19)</f>
-        <v/>
-      </c>
-      <c r="H32" s="17">
-        <f>IF('Results'!$B$17="","",'Results'!$B$17)</f>
-        <v/>
-      </c>
-      <c r="I32" s="18">
-        <f>IF('DEEP Score'!$H$32="","",IF('DEEP Score'!$H$32&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$32&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="n"/>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="E33" s="14" t="n"/>
+      <c r="F33" s="15" t="inlineStr"/>
+      <c r="G33" s="16">
+        <f>IF('Metrics'!$V$20="","",'Metrics'!$V$20)</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
+        <v/>
+      </c>
+      <c r="I33" s="18">
+        <f>IF('DEEP Score'!$H$33="","",IF('DEEP Score'!$H$33&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$33&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>Total phosphorus</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
         <is>
           <t>ug/L</t>
         </is>
       </c>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="24" t="inlineStr"/>
-      <c r="G33" s="25">
-        <f>IF('Metrics'!$V$20="","",'Metrics'!$V$20)</f>
-        <v/>
-      </c>
-      <c r="H33" s="20" t="n"/>
-      <c r="I33" s="26" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="48" t="inlineStr">
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="24" t="inlineStr"/>
+      <c r="G34" s="25">
+        <f>IF('Metrics'!$V$21="","",'Metrics'!$V$21)</f>
+        <v/>
+      </c>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
         <is>
           <t>Physicochemistry</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Water &amp; soil quality</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Std. Units</t>
         </is>
       </c>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="15" t="inlineStr"/>
-      <c r="G34" s="16">
-        <f>IF('Metrics'!$V$21="","",'Metrics'!$V$21)</f>
-        <v/>
-      </c>
-      <c r="H34" s="17">
-        <f>IF('Results'!$B$18="","",'Results'!$B$18)</f>
-        <v/>
-      </c>
-      <c r="I34" s="18">
-        <f>IF('DEEP Score'!$H$34="","",IF('DEEP Score'!$H$34&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$34&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="19" t="n"/>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="15" t="inlineStr"/>
+      <c r="G35" s="16">
+        <f>IF('Metrics'!$V$22="","",'Metrics'!$V$22)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
+        <v/>
+      </c>
+      <c r="I35" s="18">
+        <f>IF('DEEP Score'!$H$35="","",IF('DEEP Score'!$H$35&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$35&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>Turbidity</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>NTU</t>
         </is>
       </c>
-      <c r="E35" s="23" t="n"/>
-      <c r="F35" s="24" t="inlineStr"/>
-      <c r="G35" s="25">
-        <f>IF('Metrics'!$V$22="","",'Metrics'!$V$22)</f>
-        <v/>
-      </c>
-      <c r="H35" s="20" t="n"/>
-      <c r="I35" s="26" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="49" t="inlineStr">
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="24" t="inlineStr"/>
+      <c r="G36" s="25">
+        <f>IF('Metrics'!$V$23="","",'Metrics'!$V$23)</f>
+        <v/>
+      </c>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="49" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Habitat provision</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Fast-water / riffle habitat</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="15" t="inlineStr"/>
-      <c r="G36" s="16">
-        <f>IF('Metrics'!$V$23="","",'Metrics'!$V$23)</f>
-        <v/>
-      </c>
-      <c r="H36" s="17">
-        <f>IF('Results'!$B$19="","",'Results'!$B$19)</f>
-        <v/>
-      </c>
-      <c r="I36" s="18">
-        <f>IF('DEEP Score'!$H$36="","",IF('DEEP Score'!$H$36&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$36&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="19" t="n"/>
-      <c r="B37" s="20" t="n"/>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="E37" s="14" t="n"/>
+      <c r="F37" s="15" t="inlineStr"/>
+      <c r="G37" s="16">
+        <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>IF('Results'!$B$20="","",'Results'!$B$20)</f>
+        <v/>
+      </c>
+      <c r="I37" s="18">
+        <f>IF('DEEP Score'!$H$37="","",IF('DEEP Score'!$H$37&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$37&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Natural fish cover</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="E37" s="23" t="n"/>
-      <c r="F37" s="24" t="inlineStr"/>
-      <c r="G37" s="25">
-        <f>IF('Metrics'!$V$24="","",'Metrics'!$V$24)</f>
-        <v/>
-      </c>
-      <c r="H37" s="20" t="n"/>
-      <c r="I37" s="26" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="49" t="inlineStr">
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="24" t="inlineStr"/>
+      <c r="G38" s="25">
+        <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
+        <v/>
+      </c>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="49" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Population support</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Benthic total taxa richness</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="15" t="inlineStr"/>
-      <c r="G38" s="16">
-        <f>IF('Metrics'!$V$25="","",'Metrics'!$V$25)</f>
-        <v/>
-      </c>
-      <c r="H38" s="17">
-        <f>IF('Results'!$B$20="","",'Results'!$B$20)</f>
-        <v/>
-      </c>
-      <c r="I38" s="18">
-        <f>IF('DEEP Score'!$H$38="","",IF('DEEP Score'!$H$38&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$38&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="15" t="inlineStr"/>
+      <c r="G39" s="16">
+        <f>IF('Metrics'!$V$26="","",'Metrics'!$V$26)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>IF('DEEP Score'!$H$39="","",IF('DEEP Score'!$H$39&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$39&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>Native fish taxa richness</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="24" t="inlineStr"/>
-      <c r="G39" s="25">
-        <f>IF('Metrics'!$V$26="","",'Metrics'!$V$26)</f>
-        <v/>
-      </c>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="26" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="49" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="24" t="inlineStr"/>
+      <c r="G40" s="25">
+        <f>IF('Metrics'!$V$27="","",'Metrics'!$V$27)</f>
+        <v/>
+      </c>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>Community dynamics</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>EPT taxa richness</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="15" t="inlineStr"/>
-      <c r="G40" s="16">
-        <f>IF('Metrics'!$V$27="","",'Metrics'!$V$27)</f>
-        <v/>
-      </c>
-      <c r="H40" s="17">
-        <f>IF('Results'!$B$21="","",'Results'!$B$21)</f>
-        <v/>
-      </c>
-      <c r="I40" s="18">
-        <f>IF('DEEP Score'!$H$40="","",IF('DEEP Score'!$H$40&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$40&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="19" t="n"/>
-      <c r="B41" s="20" t="n"/>
-      <c r="C41" s="21" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="15" t="inlineStr"/>
+      <c r="G41" s="16">
+        <f>IF('Metrics'!$V$28="","",'Metrics'!$V$28)</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>IF('Results'!$B$22="","",'Results'!$B$22)</f>
+        <v/>
+      </c>
+      <c r="I41" s="18">
+        <f>IF('DEEP Score'!$H$41="","",IF('DEEP Score'!$H$41&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$41&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>Shannon diversity (H')</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>H'</t>
         </is>
       </c>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="24" t="inlineStr"/>
-      <c r="G41" s="25">
-        <f>IF('Metrics'!$V$28="","",'Metrics'!$V$28)</f>
-        <v/>
-      </c>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="26" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="50" t="inlineStr">
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="24" t="inlineStr"/>
+      <c r="G42" s="25">
+        <f>IF('Metrics'!$V$29="","",'Metrics'!$V$29)</f>
+        <v/>
+      </c>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="26" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="50" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="B42" s="28" t="inlineStr">
+      <c r="B43" s="28" t="inlineStr">
         <is>
           <t>Watershed connectivity</t>
         </is>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>Mapped dams within one mile</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D43" s="30" t="inlineStr">
         <is>
           <t>dams</t>
         </is>
       </c>
-      <c r="E42" s="31" t="n"/>
-      <c r="F42" s="32" t="inlineStr"/>
-      <c r="G42" s="33">
-        <f>IF('Metrics'!$V$29="","",'Metrics'!$V$29)</f>
-        <v/>
-      </c>
-      <c r="H42" s="34">
-        <f>IF('Results'!$B$22="","",'Results'!$B$22)</f>
-        <v/>
-      </c>
-      <c r="I42" s="35">
-        <f>IF('DEEP Score'!$H$42="","",IF('DEEP Score'!$H$42&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$42&lt;=10,"Functioning At-Risk","Functioning")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="51" t="inlineStr">
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="32" t="inlineStr"/>
+      <c r="G43" s="33">
+        <f>IF('Metrics'!$V$30="","",'Metrics'!$V$30)</f>
+        <v/>
+      </c>
+      <c r="H43" s="34">
+        <f>IF('Results'!$B$23="","",'Results'!$B$23)</f>
+        <v/>
+      </c>
+      <c r="I43" s="35">
+        <f>IF('DEEP Score'!$H$43="","",IF('DEEP Score'!$H$43&lt;=5,"Non-Functioning",IF('DEEP Score'!$H$43&lt;=10,"Functioning At-Risk","Functioning")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="51" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Sub-index (0 to 1)</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="52" t="inlineStr">
-        <is>
-          <t>Physical</t>
-        </is>
-      </c>
-      <c r="B46" s="53">
-        <f>'Results'!$B$25</f>
-        <v/>
-      </c>
-      <c r="C46" s="54">
-        <f>IF('DEEP Score'!$B$46&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$46&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
-        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="52" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="B47" s="53">
@@ -2701,7 +2725,7 @@
     <row r="48">
       <c r="A48" s="52" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="B48" s="53">
@@ -2713,13 +2737,13 @@
         <v/>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="55" t="inlineStr">
-        <is>
-          <t>Ecosystem Condition Index</t>
-        </is>
-      </c>
-      <c r="B49" s="56">
+    <row r="49">
+      <c r="A49" s="52" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="B49" s="53">
         <f>'Results'!$B$28</f>
         <v/>
       </c>
@@ -2728,11 +2752,19 @@
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>This index is computed over the 19 functions this assessment scores. 1 of the 20 STAF functions are not assessed, so it is not comparable with a full-framework index and no condition class is claimed for the assessment as a whole.</t>
-        </is>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>Ecosystem Condition Index</t>
+        </is>
+      </c>
+      <c r="B50" s="56">
+        <f>'Results'!$B$29</f>
+        <v/>
+      </c>
+      <c r="C50" s="54">
+        <f>IF('DEEP Score'!$B$50&lt;=0.39,"Non-Functioning",IF('DEEP Score'!$B$50&lt;=0.69,"Functioning At-Risk","Functioning"))</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2742,14 +2774,14 @@
         </is>
       </c>
       <c r="B51" s="4">
-        <f>COUNT('Results'!$B$4:$B$22)&amp;" of 19"</f>
+        <f>COUNT('Results'!$B$4:$B$23)&amp;" of 20"</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>This assessment covers 19 of 20 STAF functions (1 documented exclusions).</t>
+          <t>This assessment covers 20 of 20 STAF functions.</t>
         </is>
       </c>
     </row>
@@ -2799,56 +2831,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Wetland</t>
+          <t>Residual pool depth</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Surface water storage</t>
+          <t>Low flow and baseflow dynamics</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Residual pool depth</t>
+          <t>Bankfull height above channel</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Low flow and baseflow dynamics</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Bankfull height above channel</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
           <t>Floodplain connectivity, Channel evolution</t>
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A62" s="58" t="n"/>
+      <c r="B62" s="59" t="n"/>
+      <c r="C62" s="59" t="n"/>
+      <c r="D62" s="59" t="n"/>
+      <c r="E62" s="59" t="n"/>
+      <c r="F62" s="59" t="n"/>
+      <c r="G62" s="59" t="n"/>
+      <c r="H62" s="59" t="n"/>
+      <c r="I62" s="60" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="58" t="n"/>
-      <c r="B63" s="59" t="n"/>
-      <c r="C63" s="59" t="n"/>
-      <c r="D63" s="59" t="n"/>
-      <c r="E63" s="59" t="n"/>
-      <c r="F63" s="59" t="n"/>
-      <c r="G63" s="59" t="n"/>
-      <c r="H63" s="59" t="n"/>
-      <c r="I63" s="60" t="n"/>
+      <c r="A63" s="61" t="n"/>
+      <c r="B63" s="62" t="n"/>
+      <c r="C63" s="62" t="n"/>
+      <c r="D63" s="62" t="n"/>
+      <c r="E63" s="62" t="n"/>
+      <c r="F63" s="62" t="n"/>
+      <c r="G63" s="62" t="n"/>
+      <c r="H63" s="62" t="n"/>
+      <c r="I63" s="63" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="61" t="n"/>
@@ -2884,87 +2915,75 @@
       <c r="I66" s="63" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="61" t="n"/>
-      <c r="B67" s="62" t="n"/>
-      <c r="C67" s="62" t="n"/>
-      <c r="D67" s="62" t="n"/>
-      <c r="E67" s="62" t="n"/>
-      <c r="F67" s="62" t="n"/>
-      <c r="G67" s="62" t="n"/>
-      <c r="H67" s="62" t="n"/>
-      <c r="I67" s="63" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="64" t="n"/>
-      <c r="B68" s="65" t="n"/>
-      <c r="C68" s="65" t="n"/>
-      <c r="D68" s="65" t="n"/>
-      <c r="E68" s="65" t="n"/>
-      <c r="F68" s="65" t="n"/>
-      <c r="G68" s="65" t="n"/>
-      <c r="H68" s="65" t="n"/>
-      <c r="I68" s="66" t="n"/>
+      <c r="A67" s="64" t="n"/>
+      <c r="B67" s="65" t="n"/>
+      <c r="C67" s="65" t="n"/>
+      <c r="D67" s="65" t="n"/>
+      <c r="E67" s="65" t="n"/>
+      <c r="F67" s="65" t="n"/>
+      <c r="G67" s="65" t="n"/>
+      <c r="H67" s="65" t="n"/>
+      <c r="I67" s="66" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CB3B"/>
-  <mergeCells count="55">
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="I32:I33"/>
-    <mergeCell ref="A24:A25"/>
+  <mergeCells count="54">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="H29:H30"/>
     <mergeCell ref="B12:B13"/>
-    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="H34:H35"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="A63:I68"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="I25:I26"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A62:I67"/>
     <mergeCell ref="I12:I13"/>
+    <mergeCell ref="H22:H23"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H16:H17"/>
     <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="H37:H38"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="I34:I35"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="H35:H36"/>
   </mergeCells>
-  <conditionalFormatting sqref="G12:G42">
+  <conditionalFormatting sqref="G12:G43">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(G12),G12&lt;=0.39)</formula>
     </cfRule>
@@ -2975,7 +2994,7 @@
       <formula>AND(ISNUMBER(G12),G12&gt;0.69)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12:H42">
+  <conditionalFormatting sqref="H12:H43">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>AND(ISNUMBER(H12),H12&lt;=5)</formula>
     </cfRule>
@@ -2986,7 +3005,7 @@
       <formula>AND(ISNUMBER(H12),H12&gt;10)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I42">
+  <conditionalFormatting sqref="I12:I43">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>I12="Non-Functioning"</formula>
     </cfRule>
@@ -2998,7 +3017,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Curve set" error="Choose a curve set from the list." type="list">
+    <dataValidation sqref="F27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Curve set" error="Choose a curve set from the list." type="list">
       <formula1>=strata_spring_phab_lrbs_use</formula1>
     </dataValidation>
   </dataValidations>
@@ -3013,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3332,7 +3351,7 @@
     <row r="7">
       <c r="A7" s="68" t="inlineStr">
         <is>
-          <t>Road density</t>
+          <t>Wetland</t>
         </is>
       </c>
       <c r="B7" s="69">
@@ -3344,11 +3363,11 @@
         <v/>
       </c>
       <c r="D7" s="69">
-        <f>"spring_rddensws|"&amp;'Metrics'!$C$7</f>
+        <f>"spring_pctwet2019ws|"&amp;'Metrics'!$C$7</f>
         <v/>
       </c>
       <c r="E7" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$7,curve_key,0),MATCH("spring_rddensws|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$7,curve_key,0),MATCH("spring_pctwet2019ws|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F7" s="69">
@@ -3423,7 +3442,7 @@
     <row r="8">
       <c r="A8" s="68" t="inlineStr">
         <is>
-          <t>Base flow index</t>
+          <t>Road density</t>
         </is>
       </c>
       <c r="B8" s="69">
@@ -3435,11 +3454,11 @@
         <v/>
       </c>
       <c r="D8" s="69">
-        <f>"spring_bfiws|"&amp;'Metrics'!$C$8</f>
+        <f>"spring_rddensws|"&amp;'Metrics'!$C$8</f>
         <v/>
       </c>
       <c r="E8" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$8,curve_key,0),MATCH("spring_bfiws|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$8,curve_key,0),MATCH("spring_rddensws|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F8" s="69">
@@ -3514,7 +3533,7 @@
     <row r="9">
       <c r="A9" s="68" t="inlineStr">
         <is>
-          <t>Degree of regulation</t>
+          <t>Base flow index</t>
         </is>
       </c>
       <c r="B9" s="69">
@@ -3526,11 +3545,11 @@
         <v/>
       </c>
       <c r="D9" s="69">
-        <f>"spring_dorws|"&amp;'Metrics'!$C$9</f>
+        <f>"spring_bfiws|"&amp;'Metrics'!$C$9</f>
         <v/>
       </c>
       <c r="E9" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$9,curve_key,0),MATCH("spring_dorws|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$9,curve_key,0),MATCH("spring_bfiws|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F9" s="69">
@@ -3605,11 +3624,11 @@
     <row r="10">
       <c r="A10" s="68" t="inlineStr">
         <is>
-          <t>Bankfull width:depth ratio</t>
+          <t>Degree of regulation</t>
         </is>
       </c>
       <c r="B10" s="69">
-        <f>IF('DEEP Score'!$E$18="","",'DEEP Score'!$E$18)</f>
+        <f>IF('DEEP Score'!$E$17="","",'DEEP Score'!$E$17)</f>
         <v/>
       </c>
       <c r="C10" s="69">
@@ -3617,11 +3636,11 @@
         <v/>
       </c>
       <c r="D10" s="69">
-        <f>"spring_phab_bfwd_rat|"&amp;'Metrics'!$C$10</f>
+        <f>"spring_dorws|"&amp;'Metrics'!$C$10</f>
         <v/>
       </c>
       <c r="E10" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$10,curve_key,0),MATCH("spring_phab_bfwd_rat|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$10,curve_key,0),MATCH("spring_dorws|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F10" s="69">
@@ -3696,11 +3715,11 @@
     <row r="11">
       <c r="A11" s="68" t="inlineStr">
         <is>
-          <t>Sand + fines</t>
+          <t>Bankfull width:depth ratio</t>
         </is>
       </c>
       <c r="B11" s="69">
-        <f>IF('DEEP Score'!$E$21="","",'DEEP Score'!$E$21)</f>
+        <f>IF('DEEP Score'!$E$19="","",'DEEP Score'!$E$19)</f>
         <v/>
       </c>
       <c r="C11" s="69">
@@ -3708,11 +3727,11 @@
         <v/>
       </c>
       <c r="D11" s="69">
-        <f>"spring_phab_pct_safn|"&amp;'Metrics'!$C$11</f>
+        <f>"spring_phab_bfwd_rat|"&amp;'Metrics'!$C$11</f>
         <v/>
       </c>
       <c r="E11" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$11,curve_key,0),MATCH("spring_phab_pct_safn|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$11,curve_key,0),MATCH("spring_phab_bfwd_rat|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F11" s="69">
@@ -3787,7 +3806,7 @@
     <row r="12">
       <c r="A12" s="68" t="inlineStr">
         <is>
-          <t>Embeddedness</t>
+          <t>Sand + fines</t>
         </is>
       </c>
       <c r="B12" s="69">
@@ -3799,11 +3818,11 @@
         <v/>
       </c>
       <c r="D12" s="69">
-        <f>"spring_phab_xembed|"&amp;'Metrics'!$C$12</f>
+        <f>"spring_phab_pct_safn|"&amp;'Metrics'!$C$12</f>
         <v/>
       </c>
       <c r="E12" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$12,curve_key,0),MATCH("spring_phab_xembed|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$12,curve_key,0),MATCH("spring_phab_pct_safn|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F12" s="69">
@@ -3878,11 +3897,11 @@
     <row r="13">
       <c r="A13" s="68" t="inlineStr">
         <is>
-          <t>Sinuosity</t>
+          <t>Embeddedness</t>
         </is>
       </c>
       <c r="B13" s="69">
-        <f>IF('DEEP Score'!$E$24="","",'DEEP Score'!$E$24)</f>
+        <f>IF('DEEP Score'!$E$23="","",'DEEP Score'!$E$23)</f>
         <v/>
       </c>
       <c r="C13" s="69">
@@ -3890,11 +3909,11 @@
         <v/>
       </c>
       <c r="D13" s="69">
-        <f>"spring_phab_sinu|"&amp;'Metrics'!$C$13</f>
+        <f>"spring_phab_xembed|"&amp;'Metrics'!$C$13</f>
         <v/>
       </c>
       <c r="E13" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$13,curve_key,0),MATCH("spring_phab_sinu|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$13,curve_key,0),MATCH("spring_phab_xembed|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F13" s="69">
@@ -3969,7 +3988,7 @@
     <row r="14">
       <c r="A14" s="68" t="inlineStr">
         <is>
-          <t>Bank angle</t>
+          <t>Sinuosity</t>
         </is>
       </c>
       <c r="B14" s="69">
@@ -3981,11 +4000,11 @@
         <v/>
       </c>
       <c r="D14" s="69">
-        <f>"spring_phab_xbka|"&amp;'Metrics'!$C$14</f>
+        <f>"spring_phab_sinu|"&amp;'Metrics'!$C$14</f>
         <v/>
       </c>
       <c r="E14" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$14,curve_key,0),MATCH("spring_phab_xbka|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$14,curve_key,0),MATCH("spring_phab_sinu|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F14" s="69">
@@ -4060,7 +4079,7 @@
     <row r="15">
       <c r="A15" s="68" t="inlineStr">
         <is>
-          <t>Relative bed stability</t>
+          <t>Bank angle</t>
         </is>
       </c>
       <c r="B15" s="69">
@@ -4068,15 +4087,15 @@
         <v/>
       </c>
       <c r="C15" s="69">
-        <f>IF('DEEP Score'!$F$26="","All streams (pooled)",'DEEP Score'!$F$26)</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="D15" s="69">
-        <f>"spring_phab_lrbs_use|"&amp;'Metrics'!$C$15</f>
+        <f>"spring_phab_xbka|"&amp;'Metrics'!$C$15</f>
         <v/>
       </c>
       <c r="E15" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$15,curve_key,0),MATCH("spring_phab_lrbs_use|All streams (pooled)",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$15,curve_key,0),MATCH("spring_phab_xbka|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F15" s="69">
@@ -4151,23 +4170,23 @@
     <row r="16">
       <c r="A16" s="68" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
+          <t>Relative bed stability</t>
         </is>
       </c>
       <c r="B16" s="69">
-        <f>IF('DEEP Score'!$E$28="","",'DEEP Score'!$E$28)</f>
+        <f>IF('DEEP Score'!$E$27="","",'DEEP Score'!$E$27)</f>
         <v/>
       </c>
       <c r="C16" s="69">
-        <f>""</f>
+        <f>IF('DEEP Score'!$F$27="","All streams (pooled)",'DEEP Score'!$F$27)</f>
         <v/>
       </c>
       <c r="D16" s="69">
-        <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$16</f>
+        <f>"spring_phab_lrbs_use|"&amp;'Metrics'!$C$16</f>
         <v/>
       </c>
       <c r="E16" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$16,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$16,curve_key,0),MATCH("spring_phab_lrbs_use|All streams (pooled)",curve_key,0))</f>
         <v/>
       </c>
       <c r="F16" s="69">
@@ -4242,11 +4261,11 @@
     <row r="17">
       <c r="A17" s="68" t="inlineStr">
         <is>
-          <t>Canopy density, mid-channel</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="B17" s="69">
-        <f>IF('DEEP Score'!$E$30="","",'DEEP Score'!$E$30)</f>
+        <f>IF('DEEP Score'!$E$29="","",'DEEP Score'!$E$29)</f>
         <v/>
       </c>
       <c r="C17" s="69">
@@ -4254,11 +4273,11 @@
         <v/>
       </c>
       <c r="D17" s="69">
-        <f>"spring_phab_xcdenmid|"&amp;'Metrics'!$C$17</f>
+        <f>"spring_phab_lwdeqvolm100|"&amp;'Metrics'!$C$17</f>
         <v/>
       </c>
       <c r="E17" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$17,curve_key,0),MATCH("spring_phab_xcdenmid|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$17,curve_key,0),MATCH("spring_phab_lwdeqvolm100|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F17" s="69">
@@ -4333,7 +4352,7 @@
     <row r="18">
       <c r="A18" s="68" t="inlineStr">
         <is>
-          <t>Riparian veg cover, woody</t>
+          <t>Canopy density, mid-channel</t>
         </is>
       </c>
       <c r="B18" s="69">
@@ -4345,11 +4364,11 @@
         <v/>
       </c>
       <c r="D18" s="69">
-        <f>"spring_phab_xcmgw|"&amp;'Metrics'!$C$18</f>
+        <f>"spring_phab_xcdenmid|"&amp;'Metrics'!$C$18</f>
         <v/>
       </c>
       <c r="E18" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$18,curve_key,0),MATCH("spring_phab_xcmgw|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$18,curve_key,0),MATCH("spring_phab_xcdenmid|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F18" s="69">
@@ -4424,7 +4443,7 @@
     <row r="19">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t>Total nitrogen</t>
+          <t>Riparian veg cover, woody</t>
         </is>
       </c>
       <c r="B19" s="69">
@@ -4436,11 +4455,11 @@
         <v/>
       </c>
       <c r="D19" s="69">
-        <f>"spring_chem_ntl|"&amp;'Metrics'!$C$19</f>
+        <f>"spring_phab_xcmgw|"&amp;'Metrics'!$C$19</f>
         <v/>
       </c>
       <c r="E19" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_chem_ntl|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$19,curve_key,0),MATCH("spring_phab_xcmgw|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F19" s="69">
@@ -4515,7 +4534,7 @@
     <row r="20">
       <c r="A20" s="68" t="inlineStr">
         <is>
-          <t>Total phosphorus</t>
+          <t>Total nitrogen</t>
         </is>
       </c>
       <c r="B20" s="69">
@@ -4527,11 +4546,11 @@
         <v/>
       </c>
       <c r="D20" s="69">
-        <f>"spring_chem_ptl|"&amp;'Metrics'!$C$20</f>
+        <f>"spring_chem_ntl|"&amp;'Metrics'!$C$20</f>
         <v/>
       </c>
       <c r="E20" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$20,curve_key,0),MATCH("spring_chem_ntl|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F20" s="69">
@@ -4606,7 +4625,7 @@
     <row r="21">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Total phosphorus</t>
         </is>
       </c>
       <c r="B21" s="69">
@@ -4618,11 +4637,11 @@
         <v/>
       </c>
       <c r="D21" s="69">
-        <f>"spring_chem_ph|"&amp;'Metrics'!$C$21</f>
+        <f>"spring_chem_ptl|"&amp;'Metrics'!$C$21</f>
         <v/>
       </c>
       <c r="E21" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$21,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$21,curve_key,0),MATCH("spring_chem_ptl|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F21" s="69">
@@ -4697,7 +4716,7 @@
     <row r="22">
       <c r="A22" s="68" t="inlineStr">
         <is>
-          <t>Turbidity</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="B22" s="69">
@@ -4709,11 +4728,11 @@
         <v/>
       </c>
       <c r="D22" s="69">
-        <f>"spring_chem_turb|"&amp;'Metrics'!$C$22</f>
+        <f>"spring_chem_ph|"&amp;'Metrics'!$C$22</f>
         <v/>
       </c>
       <c r="E22" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$22,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$22,curve_key,0),MATCH("spring_chem_ph|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F22" s="69">
@@ -4788,7 +4807,7 @@
     <row r="23">
       <c r="A23" s="68" t="inlineStr">
         <is>
-          <t>Fast-water / riffle habitat</t>
+          <t>Turbidity</t>
         </is>
       </c>
       <c r="B23" s="69">
@@ -4800,11 +4819,11 @@
         <v/>
       </c>
       <c r="D23" s="69">
-        <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$23</f>
+        <f>"spring_chem_turb|"&amp;'Metrics'!$C$23</f>
         <v/>
       </c>
       <c r="E23" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$23,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$23,curve_key,0),MATCH("spring_chem_turb|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F23" s="69">
@@ -4879,7 +4898,7 @@
     <row r="24">
       <c r="A24" s="68" t="inlineStr">
         <is>
-          <t>Natural fish cover</t>
+          <t>Fast-water / riffle habitat</t>
         </is>
       </c>
       <c r="B24" s="69">
@@ -4891,11 +4910,11 @@
         <v/>
       </c>
       <c r="D24" s="69">
-        <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$24</f>
+        <f>"spring_phab_pct_fast|"&amp;'Metrics'!$C$24</f>
         <v/>
       </c>
       <c r="E24" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$24,curve_key,0),MATCH("spring_phab_pct_fast|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F24" s="69">
@@ -4970,7 +4989,7 @@
     <row r="25">
       <c r="A25" s="68" t="inlineStr">
         <is>
-          <t>Benthic total taxa richness</t>
+          <t>Natural fish cover</t>
         </is>
       </c>
       <c r="B25" s="69">
@@ -4982,11 +5001,11 @@
         <v/>
       </c>
       <c r="D25" s="69">
-        <f>"spring_bent_totlntax|"&amp;'Metrics'!$C$25</f>
+        <f>"spring_phab_xfc_nat|"&amp;'Metrics'!$C$25</f>
         <v/>
       </c>
       <c r="E25" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_bent_totlntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$25,curve_key,0),MATCH("spring_phab_xfc_nat|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F25" s="69">
@@ -5061,7 +5080,7 @@
     <row r="26">
       <c r="A26" s="68" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
+          <t>Benthic total taxa richness</t>
         </is>
       </c>
       <c r="B26" s="69">
@@ -5073,11 +5092,11 @@
         <v/>
       </c>
       <c r="D26" s="69">
-        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$26</f>
+        <f>"spring_bent_totlntax|"&amp;'Metrics'!$C$26</f>
         <v/>
       </c>
       <c r="E26" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_fish_nat_totlntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$26,curve_key,0),MATCH("spring_bent_totlntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F26" s="69">
@@ -5152,7 +5171,7 @@
     <row r="27">
       <c r="A27" s="68" t="inlineStr">
         <is>
-          <t>EPT taxa richness</t>
+          <t>Native fish taxa richness</t>
         </is>
       </c>
       <c r="B27" s="69">
@@ -5164,11 +5183,11 @@
         <v/>
       </c>
       <c r="D27" s="69">
-        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$27</f>
+        <f>"spring_fish_nat_totlntax|"&amp;'Metrics'!$C$27</f>
         <v/>
       </c>
       <c r="E27" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$27,curve_key,0),MATCH("spring_fish_nat_totlntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F27" s="69">
@@ -5243,7 +5262,7 @@
     <row r="28">
       <c r="A28" s="68" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
+          <t>EPT taxa richness</t>
         </is>
       </c>
       <c r="B28" s="69">
@@ -5255,11 +5274,11 @@
         <v/>
       </c>
       <c r="D28" s="69">
-        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$28</f>
+        <f>"spring_bent_ept_ntax|"&amp;'Metrics'!$C$28</f>
         <v/>
       </c>
       <c r="E28" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$28,curve_key,0),MATCH("spring_bent_ept_ntax|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F28" s="69">
@@ -5334,7 +5353,7 @@
     <row r="29">
       <c r="A29" s="68" t="inlineStr">
         <is>
-          <t>Mapped dams within one mile</t>
+          <t>Shannon diversity (H')</t>
         </is>
       </c>
       <c r="B29" s="69">
@@ -5346,11 +5365,11 @@
         <v/>
       </c>
       <c r="D29" s="69">
-        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$29</f>
+        <f>"spring_bent_hprime|"&amp;'Metrics'!$C$29</f>
         <v/>
       </c>
       <c r="E29" s="69">
-        <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
+        <f>IFERROR(MATCH('Metrics'!$D$29,curve_key,0),MATCH("spring_bent_hprime|",curve_key,0))</f>
         <v/>
       </c>
       <c r="F29" s="69">
@@ -5419,6 +5438,97 @@
       </c>
       <c r="V29" s="70">
         <f>IF(ISNUMBER('Metrics'!$B$29),MAX(0,MIN(1,IF('Metrics'!$B$29&lt;='Metrics'!$F$29,'Metrics'!$N$29,IF('Metrics'!$B$29&gt;='Metrics'!$M$29,'Metrics'!$U$29,IF('Metrics'!$B$29&lt;='Metrics'!$G$29,IF('Metrics'!$G$29-'Metrics'!$F$29&lt;=0,'Metrics'!$O$29,'Metrics'!$N$29+('Metrics'!$B$29-'Metrics'!$F$29)/('Metrics'!$G$29-'Metrics'!$F$29)*('Metrics'!$O$29-'Metrics'!$N$29)),IF('Metrics'!$B$29&lt;='Metrics'!$H$29,IF('Metrics'!$H$29-'Metrics'!$G$29&lt;=0,'Metrics'!$P$29,'Metrics'!$O$29+('Metrics'!$B$29-'Metrics'!$G$29)/('Metrics'!$H$29-'Metrics'!$G$29)*('Metrics'!$P$29-'Metrics'!$O$29)),IF('Metrics'!$B$29&lt;='Metrics'!$I$29,IF('Metrics'!$I$29-'Metrics'!$H$29&lt;=0,'Metrics'!$Q$29,'Metrics'!$P$29+('Metrics'!$B$29-'Metrics'!$H$29)/('Metrics'!$I$29-'Metrics'!$H$29)*('Metrics'!$Q$29-'Metrics'!$P$29)),IF('Metrics'!$B$29&lt;='Metrics'!$J$29,IF('Metrics'!$J$29-'Metrics'!$I$29&lt;=0,'Metrics'!$R$29,'Metrics'!$Q$29+('Metrics'!$B$29-'Metrics'!$I$29)/('Metrics'!$J$29-'Metrics'!$I$29)*('Metrics'!$R$29-'Metrics'!$Q$29)),IF('Metrics'!$B$29&lt;='Metrics'!$K$29,IF('Metrics'!$K$29-'Metrics'!$J$29&lt;=0,'Metrics'!$S$29,'Metrics'!$R$29+('Metrics'!$B$29-'Metrics'!$J$29)/('Metrics'!$K$29-'Metrics'!$J$29)*('Metrics'!$S$29-'Metrics'!$R$29)),IF('Metrics'!$B$29&lt;='Metrics'!$L$29,IF('Metrics'!$L$29-'Metrics'!$K$29&lt;=0,'Metrics'!$T$29,'Metrics'!$S$29+('Metrics'!$B$29-'Metrics'!$K$29)/('Metrics'!$L$29-'Metrics'!$K$29)*('Metrics'!$T$29-'Metrics'!$S$29)),IF('Metrics'!$M$29-'Metrics'!$L$29&lt;=0,'Metrics'!$U$29,'Metrics'!$T$29+('Metrics'!$B$29-'Metrics'!$L$29)/('Metrics'!$M$29-'Metrics'!$L$29)*('Metrics'!$U$29-'Metrics'!$T$29)))))))))))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="68" t="inlineStr">
+        <is>
+          <t>Mapped dams within one mile</t>
+        </is>
+      </c>
+      <c r="B30" s="69">
+        <f>IF('DEEP Score'!$E$43="","",'DEEP Score'!$E$43)</f>
+        <v/>
+      </c>
+      <c r="C30" s="69">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D30" s="69">
+        <f>"spring_nid_dams_1mi|"&amp;'Metrics'!$C$30</f>
+        <v/>
+      </c>
+      <c r="E30" s="69">
+        <f>IFERROR(MATCH('Metrics'!$D$30,curve_key,0),MATCH("spring_nid_dams_1mi|",curve_key,0))</f>
+        <v/>
+      </c>
+      <c r="F30" s="69">
+        <f>INDEX(curve_x1,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="69">
+        <f>INDEX(curve_x2,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="69">
+        <f>INDEX(curve_x3,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="69">
+        <f>INDEX(curve_x4,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="69">
+        <f>INDEX(curve_x5,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="69">
+        <f>INDEX(curve_x6,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="69">
+        <f>INDEX(curve_x7,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="69">
+        <f>INDEX(curve_x8,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="69">
+        <f>INDEX(curve_y1,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="69">
+        <f>INDEX(curve_y2,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="P30" s="69">
+        <f>INDEX(curve_y3,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="69">
+        <f>INDEX(curve_y4,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="R30" s="69">
+        <f>INDEX(curve_y5,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="S30" s="69">
+        <f>INDEX(curve_y6,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="T30" s="69">
+        <f>INDEX(curve_y7,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="U30" s="69">
+        <f>INDEX(curve_y8,'Metrics'!$E$30)</f>
+        <v/>
+      </c>
+      <c r="V30" s="70">
+        <f>IF(ISNUMBER('Metrics'!$B$30),MAX(0,MIN(1,IF('Metrics'!$B$30&lt;='Metrics'!$F$30,'Metrics'!$N$30,IF('Metrics'!$B$30&gt;='Metrics'!$M$30,'Metrics'!$U$30,IF('Metrics'!$B$30&lt;='Metrics'!$G$30,IF('Metrics'!$G$30-'Metrics'!$F$30&lt;=0,'Metrics'!$O$30,'Metrics'!$N$30+('Metrics'!$B$30-'Metrics'!$F$30)/('Metrics'!$G$30-'Metrics'!$F$30)*('Metrics'!$O$30-'Metrics'!$N$30)),IF('Metrics'!$B$30&lt;='Metrics'!$H$30,IF('Metrics'!$H$30-'Metrics'!$G$30&lt;=0,'Metrics'!$P$30,'Metrics'!$O$30+('Metrics'!$B$30-'Metrics'!$G$30)/('Metrics'!$H$30-'Metrics'!$G$30)*('Metrics'!$P$30-'Metrics'!$O$30)),IF('Metrics'!$B$30&lt;='Metrics'!$I$30,IF('Metrics'!$I$30-'Metrics'!$H$30&lt;=0,'Metrics'!$Q$30,'Metrics'!$P$30+('Metrics'!$B$30-'Metrics'!$H$30)/('Metrics'!$I$30-'Metrics'!$H$30)*('Metrics'!$Q$30-'Metrics'!$P$30)),IF('Metrics'!$B$30&lt;='Metrics'!$J$30,IF('Metrics'!$J$30-'Metrics'!$I$30&lt;=0,'Metrics'!$R$30,'Metrics'!$Q$30+('Metrics'!$B$30-'Metrics'!$I$30)/('Metrics'!$J$30-'Metrics'!$I$30)*('Metrics'!$R$30-'Metrics'!$Q$30)),IF('Metrics'!$B$30&lt;='Metrics'!$K$30,IF('Metrics'!$K$30-'Metrics'!$J$30&lt;=0,'Metrics'!$S$30,'Metrics'!$R$30+('Metrics'!$B$30-'Metrics'!$J$30)/('Metrics'!$K$30-'Metrics'!$J$30)*('Metrics'!$S$30-'Metrics'!$R$30)),IF('Metrics'!$B$30&lt;='Metrics'!$L$30,IF('Metrics'!$L$30-'Metrics'!$K$30&lt;=0,'Metrics'!$T$30,'Metrics'!$S$30+('Metrics'!$B$30-'Metrics'!$K$30)/('Metrics'!$L$30-'Metrics'!$K$30)*('Metrics'!$T$30-'Metrics'!$S$30)),IF('Metrics'!$M$30-'Metrics'!$L$30&lt;=0,'Metrics'!$U$30,'Metrics'!$T$30+('Metrics'!$B$30-'Metrics'!$L$30)/('Metrics'!$M$30-'Metrics'!$L$30)*('Metrics'!$U$30-'Metrics'!$T$30)))))))))))),"")</f>
         <v/>
       </c>
     </row>
@@ -5434,7 +5544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5551,7 +5661,7 @@
     <row r="5">
       <c r="A5" s="68" t="inlineStr">
         <is>
-          <t>Reach inflow</t>
+          <t>Surface water storage</t>
         </is>
       </c>
       <c r="B5" s="69">
@@ -5595,11 +5705,11 @@
     <row r="6">
       <c r="A6" s="68" t="inlineStr">
         <is>
-          <t>Streamflow regime</t>
+          <t>Reach inflow</t>
         </is>
       </c>
       <c r="B6" s="69">
-        <f>IF(COUNT('DEEP Score'!G15:G16)=0,"",SUM('DEEP Score'!G15:G16)/COUNT('DEEP Score'!G15:G16)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G15:G15)=0,"",SUM('DEEP Score'!G15:G15)/COUNT('DEEP Score'!G15:G15)*15)</f>
         <v/>
       </c>
       <c r="C6" s="68" t="n">
@@ -5639,11 +5749,11 @@
     <row r="7">
       <c r="A7" s="68" t="inlineStr">
         <is>
-          <t>Low flow and baseflow dynamics</t>
+          <t>Streamflow regime</t>
         </is>
       </c>
       <c r="B7" s="69">
-        <f>IF(COUNT('DEEP Score'!G17:G18)=0,"",SUM('DEEP Score'!G17:G18)/COUNT('DEEP Score'!G17:G18)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G16:G17)=0,"",SUM('DEEP Score'!G16:G17)/COUNT('DEEP Score'!G16:G17)*15)</f>
         <v/>
       </c>
       <c r="C7" s="68" t="n">
@@ -5683,11 +5793,11 @@
     <row r="8">
       <c r="A8" s="68" t="inlineStr">
         <is>
-          <t>High flow dynamics</t>
+          <t>Low flow and baseflow dynamics</t>
         </is>
       </c>
       <c r="B8" s="69">
-        <f>IF(COUNT('DEEP Score'!G19:G19)=0,"",SUM('DEEP Score'!G19:G19)/COUNT('DEEP Score'!G19:G19)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G18:G19)=0,"",SUM('DEEP Score'!G18:G19)/COUNT('DEEP Score'!G18:G19)*15)</f>
         <v/>
       </c>
       <c r="C8" s="68" t="n">
@@ -5727,7 +5837,7 @@
     <row r="9">
       <c r="A9" s="68" t="inlineStr">
         <is>
-          <t>Floodplain connectivity</t>
+          <t>High flow dynamics</t>
         </is>
       </c>
       <c r="B9" s="69">
@@ -5771,11 +5881,11 @@
     <row r="10">
       <c r="A10" s="68" t="inlineStr">
         <is>
-          <t>Hyporheic connectivity</t>
+          <t>Floodplain connectivity</t>
         </is>
       </c>
       <c r="B10" s="69">
-        <f>IF(COUNT('DEEP Score'!G21:G22)=0,"",SUM('DEEP Score'!G21:G22)/COUNT('DEEP Score'!G21:G22)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G21:G21)=0,"",SUM('DEEP Score'!G21:G21)/COUNT('DEEP Score'!G21:G21)*15)</f>
         <v/>
       </c>
       <c r="C10" s="68" t="n">
@@ -5815,11 +5925,11 @@
     <row r="11">
       <c r="A11" s="68" t="inlineStr">
         <is>
-          <t>Channel evolution</t>
+          <t>Hyporheic connectivity</t>
         </is>
       </c>
       <c r="B11" s="69">
-        <f>IF(COUNT('DEEP Score'!G23:G23)=0,"",SUM('DEEP Score'!G23:G23)/COUNT('DEEP Score'!G23:G23)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G22:G23)=0,"",SUM('DEEP Score'!G22:G23)/COUNT('DEEP Score'!G22:G23)*15)</f>
         <v/>
       </c>
       <c r="C11" s="68" t="n">
@@ -5859,11 +5969,11 @@
     <row r="12">
       <c r="A12" s="68" t="inlineStr">
         <is>
-          <t>Channel and floodplain dynamics</t>
+          <t>Channel evolution</t>
         </is>
       </c>
       <c r="B12" s="69">
-        <f>IF(COUNT('DEEP Score'!G24:G25)=0,"",SUM('DEEP Score'!G24:G25)/COUNT('DEEP Score'!G24:G25)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G24:G24)=0,"",SUM('DEEP Score'!G24:G24)/COUNT('DEEP Score'!G24:G24)*15)</f>
         <v/>
       </c>
       <c r="C12" s="68" t="n">
@@ -5903,11 +6013,11 @@
     <row r="13">
       <c r="A13" s="68" t="inlineStr">
         <is>
-          <t>Sediment continuity</t>
+          <t>Channel and floodplain dynamics</t>
         </is>
       </c>
       <c r="B13" s="69">
-        <f>IF(COUNT('DEEP Score'!G26:G27)=0,"",SUM('DEEP Score'!G26:G27)/COUNT('DEEP Score'!G26:G27)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G25:G26)=0,"",SUM('DEEP Score'!G25:G26)/COUNT('DEEP Score'!G25:G26)*15)</f>
         <v/>
       </c>
       <c r="C13" s="68" t="n">
@@ -5947,11 +6057,11 @@
     <row r="14">
       <c r="A14" s="68" t="inlineStr">
         <is>
-          <t>Bed composition and bedform dynamics</t>
+          <t>Sediment continuity</t>
         </is>
       </c>
       <c r="B14" s="69">
-        <f>IF(COUNT('DEEP Score'!G28:G29)=0,"",SUM('DEEP Score'!G28:G29)/COUNT('DEEP Score'!G28:G29)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G27:G28)=0,"",SUM('DEEP Score'!G27:G28)/COUNT('DEEP Score'!G27:G28)*15)</f>
         <v/>
       </c>
       <c r="C14" s="68" t="n">
@@ -5991,18 +6101,18 @@
     <row r="15">
       <c r="A15" s="68" t="inlineStr">
         <is>
-          <t>Light &amp; thermal regime</t>
+          <t>Bed composition and bedform dynamics</t>
         </is>
       </c>
       <c r="B15" s="69">
-        <f>IF(COUNT('DEEP Score'!G30:G30)=0,"",SUM('DEEP Score'!G30:G30)/COUNT('DEEP Score'!G30:G30)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G29:G30)=0,"",SUM('DEEP Score'!G29:G30)/COUNT('DEEP Score'!G29:G30)*15)</f>
         <v/>
       </c>
       <c r="C15" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="68" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="E15" s="68" t="n">
         <v>0.1</v>
@@ -6035,7 +6145,7 @@
     <row r="16">
       <c r="A16" s="68" t="inlineStr">
         <is>
-          <t>Carbon processing</t>
+          <t>Light &amp; thermal regime</t>
         </is>
       </c>
       <c r="B16" s="69">
@@ -6079,15 +6189,15 @@
     <row r="17">
       <c r="A17" s="68" t="inlineStr">
         <is>
-          <t>Nutrient cycling</t>
+          <t>Carbon processing</t>
         </is>
       </c>
       <c r="B17" s="69">
-        <f>IF(COUNT('DEEP Score'!G32:G33)=0,"",SUM('DEEP Score'!G32:G33)/COUNT('DEEP Score'!G32:G33)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G32:G32)=0,"",SUM('DEEP Score'!G32:G32)/COUNT('DEEP Score'!G32:G32)*15)</f>
         <v/>
       </c>
       <c r="C17" s="68" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="68" t="n">
         <v>1</v>
@@ -6123,11 +6233,11 @@
     <row r="18">
       <c r="A18" s="68" t="inlineStr">
         <is>
-          <t>Water &amp; soil quality</t>
+          <t>Nutrient cycling</t>
         </is>
       </c>
       <c r="B18" s="69">
-        <f>IF(COUNT('DEEP Score'!G34:G35)=0,"",SUM('DEEP Score'!G34:G35)/COUNT('DEEP Score'!G34:G35)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G33:G34)=0,"",SUM('DEEP Score'!G33:G34)/COUNT('DEEP Score'!G33:G34)*15)</f>
         <v/>
       </c>
       <c r="C18" s="68" t="n">
@@ -6167,21 +6277,21 @@
     <row r="19">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t>Habitat provision</t>
+          <t>Water &amp; soil quality</t>
         </is>
       </c>
       <c r="B19" s="69">
-        <f>IF(COUNT('DEEP Score'!G36:G37)=0,"",SUM('DEEP Score'!G36:G37)/COUNT('DEEP Score'!G36:G37)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G35:G36)=0,"",SUM('DEEP Score'!G35:G36)/COUNT('DEEP Score'!G35:G36)*15)</f>
         <v/>
       </c>
       <c r="C19" s="68" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D19" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="68" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F19" s="69">
         <f>IF(ISNUMBER('Results'!$B$19),'Results'!$B$19*'Results'!$C$19,0)</f>
@@ -6211,18 +6321,18 @@
     <row r="20">
       <c r="A20" s="68" t="inlineStr">
         <is>
-          <t>Population support</t>
+          <t>Habitat provision</t>
         </is>
       </c>
       <c r="B20" s="69">
-        <f>IF(COUNT('DEEP Score'!G38:G39)=0,"",SUM('DEEP Score'!G38:G39)/COUNT('DEEP Score'!G38:G39)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G37:G38)=0,"",SUM('DEEP Score'!G37:G38)/COUNT('DEEP Score'!G37:G38)*15)</f>
         <v/>
       </c>
       <c r="C20" s="68" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="68" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="68" t="n">
         <v>1</v>
@@ -6255,11 +6365,11 @@
     <row r="21">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>Community dynamics</t>
+          <t>Population support</t>
         </is>
       </c>
       <c r="B21" s="69">
-        <f>IF(COUNT('DEEP Score'!G40:G41)=0,"",SUM('DEEP Score'!G40:G41)/COUNT('DEEP Score'!G40:G41)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G39:G40)=0,"",SUM('DEEP Score'!G39:G40)/COUNT('DEEP Score'!G39:G40)*15)</f>
         <v/>
       </c>
       <c r="C21" s="68" t="n">
@@ -6299,18 +6409,18 @@
     <row r="22">
       <c r="A22" s="68" t="inlineStr">
         <is>
-          <t>Watershed connectivity</t>
+          <t>Community dynamics</t>
         </is>
       </c>
       <c r="B22" s="69">
-        <f>IF(COUNT('DEEP Score'!G42:G42)=0,"",SUM('DEEP Score'!G42:G42)/COUNT('DEEP Score'!G42:G42)*15)</f>
+        <f>IF(COUNT('DEEP Score'!G41:G42)=0,"",SUM('DEEP Score'!G41:G42)/COUNT('DEEP Score'!G41:G42)*15)</f>
         <v/>
       </c>
       <c r="C22" s="68" t="n">
         <v>0.1</v>
       </c>
       <c r="D22" s="68" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E22" s="68" t="n">
         <v>1</v>
@@ -6340,59 +6450,103 @@
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="68" t="inlineStr">
+        <is>
+          <t>Watershed connectivity</t>
+        </is>
+      </c>
+      <c r="B23" s="69">
+        <f>IF(COUNT('DEEP Score'!G43:G43)=0,"",SUM('DEEP Score'!G43:G43)/COUNT('DEEP Score'!G43:G43)*15)</f>
+        <v/>
+      </c>
+      <c r="C23" s="68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="69">
+        <f>IF(ISNUMBER('Results'!$B$23),'Results'!$B$23*'Results'!$C$23,0)</f>
+        <v/>
+      </c>
+      <c r="G23" s="69">
+        <f>IF(ISNUMBER('Results'!$B$23),'Results'!$B$23*'Results'!$D$23,0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="69">
+        <f>IF(ISNUMBER('Results'!$B$23),'Results'!$B$23*'Results'!$E$23,0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="69">
+        <f>IF(ISNUMBER('Results'!$B$23),15*'Results'!$C$23,0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="69">
+        <f>IF(ISNUMBER('Results'!$B$23),15*'Results'!$D$23,0)</f>
+        <v/>
+      </c>
+      <c r="K23" s="69">
+        <f>IF(ISNUMBER('Results'!$B$23),15*'Results'!$E$23,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Sub-index</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="68" t="inlineStr">
-        <is>
-          <t>Physical</t>
-        </is>
-      </c>
-      <c r="B25" s="69">
-        <f>IF(SUM('Results'!$I$4:$I$22)=0,0,SUM('Results'!$F$4:$F$22)/SUM('Results'!$I$4:$I$22))</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="68" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="B26" s="69">
-        <f>IF(SUM('Results'!$J$4:$J$22)=0,0,SUM('Results'!$G$4:$G$22)/SUM('Results'!$J$4:$J$22))</f>
+        <f>IF(SUM('Results'!$I$4:$I$23)=0,0,SUM('Results'!$F$4:$F$23)/SUM('Results'!$I$4:$I$23))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="68" t="inlineStr">
         <is>
+          <t>Chemical</t>
+        </is>
+      </c>
+      <c r="B27" s="69">
+        <f>IF(SUM('Results'!$J$4:$J$23)=0,0,SUM('Results'!$G$4:$G$23)/SUM('Results'!$J$4:$J$23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="68" t="inlineStr">
+        <is>
           <t>Biological</t>
         </is>
       </c>
-      <c r="B27" s="69">
-        <f>IF(SUM('Results'!$K$4:$K$22)=0,0,SUM('Results'!$H$4:$H$22)/SUM('Results'!$K$4:$K$22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="52" t="inlineStr">
+      <c r="B28" s="69">
+        <f>IF(SUM('Results'!$K$4:$K$23)=0,0,SUM('Results'!$H$4:$H$23)/SUM('Results'!$K$4:$K$23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="52" t="inlineStr">
         <is>
           <t>Ecosystem Condition Index</t>
         </is>
       </c>
-      <c r="B28" s="69">
-        <f>('Results'!$B$25+'Results'!$B$26+'Results'!$B$27)/3</f>
+      <c r="B29" s="69">
+        <f>('Results'!$B$26+'Results'!$B$27+'Results'!$B$28)/3</f>
         <v/>
       </c>
     </row>
@@ -6408,7 +6562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -6695,294 +6849,294 @@
     <row r="7">
       <c r="A7" s="68" t="inlineStr">
         <is>
-          <t>spring_rddensws|</t>
+          <t>spring_pctwet2019ws|</t>
         </is>
       </c>
       <c r="B7" s="68" t="inlineStr">
         <is>
-          <t>spring-rddensws</t>
+          <t>spring-pctwet2019ws</t>
         </is>
       </c>
       <c r="C7" s="68" t="inlineStr">
         <is>
-          <t>Road density</t>
+          <t>Wetland</t>
         </is>
       </c>
       <c r="D7" s="68" t="inlineStr"/>
       <c r="E7" s="68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="68" t="inlineStr">
         <is>
-          <t>Fixed criteria, the same in every region</t>
+          <t>18 least-disturbed stations of this ecoregion. The build refused this source (ACC-04: The pool is not stable, since one station moves a quartile by 0.21 of the interquartile range, more than 0.20). The owner accepted it with a recorded rationale.</t>
         </is>
       </c>
       <c r="G7" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="68" t="n">
-        <v>1</v>
+        <v>3.407142857142857</v>
       </c>
       <c r="I7" s="68" t="n">
-        <v>3</v>
+        <v>7.95</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>5.6</v>
+        <v>12.5525</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>5.6</v>
+        <v>13.93325</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>5.6</v>
+        <v>13.93325</v>
       </c>
       <c r="M7" s="68" t="n">
-        <v>5.6</v>
+        <v>13.93325</v>
       </c>
       <c r="N7" s="68" t="n">
-        <v>5.6</v>
+        <v>13.93325</v>
       </c>
       <c r="O7" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" s="68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" s="68" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="R7" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="68" t="inlineStr">
         <is>
-          <t>spring_bfiws|</t>
+          <t>spring_rddensws|</t>
         </is>
       </c>
       <c r="B8" s="68" t="inlineStr">
         <is>
-          <t>spring-bfiws</t>
+          <t>spring-rddensws</t>
         </is>
       </c>
       <c r="C8" s="68" t="inlineStr">
         <is>
-          <t>Base flow index</t>
+          <t>Road density</t>
         </is>
       </c>
       <c r="D8" s="68" t="inlineStr"/>
       <c r="E8" s="68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="68" t="inlineStr">
         <is>
-          <t>40 least-disturbed streams of this ecoregion under the regional screen (agriculture at most 25 percent)</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G8" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="68" t="n">
-        <v>15.04345714285714</v>
+        <v>1</v>
       </c>
       <c r="I8" s="68" t="n">
-        <v>35.1014</v>
+        <v>3</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>47.580625</v>
+        <v>5.6</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>51.32439250000001</v>
+        <v>5.6</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>51.32439250000001</v>
+        <v>5.6</v>
       </c>
       <c r="M8" s="68" t="n">
-        <v>51.32439250000001</v>
+        <v>5.6</v>
       </c>
       <c r="N8" s="68" t="n">
-        <v>51.32439250000001</v>
+        <v>5.6</v>
       </c>
       <c r="O8" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="68" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q8" s="68" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R8" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="68" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q8" s="68" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R8" s="68" t="n">
-        <v>1</v>
-      </c>
       <c r="S8" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="68" t="inlineStr">
         <is>
-          <t>spring_dorws|</t>
+          <t>spring_bfiws|</t>
         </is>
       </c>
       <c r="B9" s="68" t="inlineStr">
         <is>
-          <t>spring-dorws</t>
+          <t>spring-bfiws</t>
         </is>
       </c>
       <c r="C9" s="68" t="inlineStr">
         <is>
-          <t>Degree of regulation</t>
+          <t>Base flow index</t>
         </is>
       </c>
       <c r="D9" s="68" t="inlineStr"/>
       <c r="E9" s="68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="68" t="inlineStr">
         <is>
-          <t>Fixed criteria, the same in every region</t>
+          <t>40 least-disturbed streams of this ecoregion under the regional screen (agriculture at most 25 percent), carried forward from version 1</t>
         </is>
       </c>
       <c r="G9" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="68" t="n">
-        <v>2</v>
+        <v>15.04345714285714</v>
       </c>
       <c r="I9" s="68" t="n">
-        <v>15.005</v>
+        <v>35.1014</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>31.9115</v>
+        <v>47.580625</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>31.9115</v>
+        <v>51.32439250000001</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>31.9115</v>
+        <v>51.32439250000001</v>
       </c>
       <c r="M9" s="68" t="n">
-        <v>31.9115</v>
+        <v>51.32439250000001</v>
       </c>
       <c r="N9" s="68" t="n">
-        <v>31.9115</v>
+        <v>51.32439250000001</v>
       </c>
       <c r="O9" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="Q9" s="68" t="n">
-        <v>0.39</v>
+        <v>0.7</v>
       </c>
       <c r="R9" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_bfwd_rat|</t>
+          <t>spring_dorws|</t>
         </is>
       </c>
       <c r="B10" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-bfwd-rat</t>
+          <t>spring-dorws</t>
         </is>
       </c>
       <c r="C10" s="68" t="inlineStr">
         <is>
-          <t>Bankfull width:depth ratio</t>
+          <t>Degree of regulation</t>
         </is>
       </c>
       <c r="D10" s="68" t="inlineStr"/>
       <c r="E10" s="68" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>Fixed criteria, the same in every region</t>
         </is>
       </c>
       <c r="G10" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="68" t="n">
-        <v>0.8176608085632324</v>
+        <v>2</v>
       </c>
       <c r="I10" s="68" t="n">
-        <v>3.543718737363815</v>
+        <v>15.005</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>5.011596083641052</v>
+        <v>31.9115</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>9.205531358718872</v>
+        <v>31.9115</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>10.67340870499611</v>
+        <v>31.9115</v>
       </c>
       <c r="M10" s="68" t="n">
-        <v>13.39946663379669</v>
+        <v>31.9115</v>
       </c>
       <c r="N10" s="68" t="n">
-        <v>17.59340190887451</v>
+        <v>31.9115</v>
       </c>
       <c r="O10" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="68" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Q10" s="68" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="R10" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="68" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q10" s="68" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R10" s="68" t="n">
-        <v>1</v>
-      </c>
       <c r="S10" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" s="68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="U10" s="68" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V10" s="68" t="n">
         <v>0</v>
@@ -6991,72 +7145,72 @@
     <row r="11">
       <c r="A11" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_pct_safn|</t>
+          <t>spring_phab_bfwd_rat|</t>
         </is>
       </c>
       <c r="B11" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-pct-safn</t>
+          <t>spring-phab-bfwd-rat</t>
         </is>
       </c>
       <c r="C11" s="68" t="inlineStr">
         <is>
-          <t>Sand + fines</t>
+          <t>Bankfull width:depth ratio</t>
         </is>
       </c>
       <c r="D11" s="68" t="inlineStr"/>
       <c r="E11" s="68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G11" s="68" t="n">
-        <v>64.61904678344726</v>
+        <v>0</v>
       </c>
       <c r="H11" s="68" t="n">
-        <v>71.19047546386719</v>
+        <v>0.8176608085632324</v>
       </c>
       <c r="I11" s="68" t="n">
-        <v>93.09523773193359</v>
+        <v>3.543718737363815</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>100</v>
+        <v>5.011596083641052</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>100</v>
+        <v>9.205531358718872</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>100</v>
+        <v>10.67340870499611</v>
       </c>
       <c r="M11" s="68" t="n">
-        <v>100</v>
+        <v>13.39946663379669</v>
       </c>
       <c r="N11" s="68" t="n">
-        <v>100</v>
+        <v>17.59340190887451</v>
       </c>
       <c r="O11" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q11" s="68" t="n">
         <v>0.7</v>
       </c>
       <c r="R11" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="68" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U11" s="68" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="V11" s="68" t="n">
         <v>0</v>
@@ -7065,17 +7219,17 @@
     <row r="12">
       <c r="A12" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_xembed|</t>
+          <t>spring_phab_pct_safn|</t>
         </is>
       </c>
       <c r="B12" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-xembed</t>
+          <t>spring-phab-pct-safn</t>
         </is>
       </c>
       <c r="C12" s="68" t="inlineStr">
         <is>
-          <t>Embeddedness</t>
+          <t>Sand + fines</t>
         </is>
       </c>
       <c r="D12" s="68" t="inlineStr"/>
@@ -7084,17 +7238,17 @@
       </c>
       <c r="F12" s="68" t="inlineStr">
         <is>
-          <t>34 least-disturbed streams of this ecoregion under the regional screen (agriculture at most 25 percent)</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G12" s="68" t="n">
-        <v>66.30681533813477</v>
+        <v>64.61904678344726</v>
       </c>
       <c r="H12" s="68" t="n">
-        <v>73.70454406738281</v>
+        <v>71.19047546386719</v>
       </c>
       <c r="I12" s="68" t="n">
-        <v>98.36363983154297</v>
+        <v>93.09523773193359</v>
       </c>
       <c r="J12" s="68" t="n">
         <v>100</v>
@@ -7139,17 +7293,17 @@
     <row r="13">
       <c r="A13" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_sinu|</t>
+          <t>spring_phab_xembed|</t>
         </is>
       </c>
       <c r="B13" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-sinu</t>
+          <t>spring-phab-xembed</t>
         </is>
       </c>
       <c r="C13" s="68" t="inlineStr">
         <is>
-          <t>Sinuosity</t>
+          <t>Embeddedness</t>
         </is>
       </c>
       <c r="D13" s="68" t="inlineStr"/>
@@ -7158,109 +7312,109 @@
       </c>
       <c r="F13" s="68" t="inlineStr">
         <is>
-          <t>16 least-disturbed stations of this ecoregion</t>
+          <t>34 least-disturbed streams of this ecoregion under the regional screen (agriculture at most 25 percent), carried forward from version 1</t>
         </is>
       </c>
       <c r="G13" s="68" t="n">
-        <v>1</v>
+        <v>66.30681533813477</v>
       </c>
       <c r="H13" s="68" t="n">
-        <v>1.099091857671738</v>
+        <v>73.70454406738281</v>
       </c>
       <c r="I13" s="68" t="n">
-        <v>1.452753812074661</v>
+        <v>98.36363983154297</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>1.558852398395538</v>
+        <v>100</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>1.558852398395538</v>
+        <v>100</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>1.558852398395538</v>
+        <v>100</v>
       </c>
       <c r="M13" s="68" t="n">
-        <v>1.558852398395538</v>
+        <v>100</v>
       </c>
       <c r="N13" s="68" t="n">
-        <v>1.558852398395538</v>
+        <v>100</v>
       </c>
       <c r="O13" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R13" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="68" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q13" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="68" t="n">
-        <v>1</v>
-      </c>
       <c r="S13" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_xbka|</t>
+          <t>spring_phab_sinu|</t>
         </is>
       </c>
       <c r="B14" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-xbka</t>
+          <t>spring-phab-sinu</t>
         </is>
       </c>
       <c r="C14" s="68" t="inlineStr">
         <is>
-          <t>Bank angle</t>
+          <t>Sinuosity</t>
         </is>
       </c>
       <c r="D14" s="68" t="inlineStr"/>
       <c r="E14" s="68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F14" s="68" t="inlineStr">
         <is>
-          <t>34 least-disturbed streams of this ecoregion under the regional screen (agriculture at most 25 percent)</t>
+          <t>16 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G14" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="68" t="n">
+        <v>1.099091857671738</v>
+      </c>
+      <c r="I14" s="68" t="n">
+        <v>1.452753812074661</v>
+      </c>
+      <c r="J14" s="68" t="n">
+        <v>1.558852398395538</v>
+      </c>
+      <c r="K14" s="68" t="n">
+        <v>1.558852398395538</v>
+      </c>
+      <c r="L14" s="68" t="n">
+        <v>1.558852398395538</v>
+      </c>
+      <c r="M14" s="68" t="n">
+        <v>1.558852398395538</v>
+      </c>
+      <c r="N14" s="68" t="n">
+        <v>1.558852398395538</v>
+      </c>
+      <c r="O14" s="68" t="n">
         <v>0</v>
-      </c>
-      <c r="H14" s="68" t="n">
-        <v>23.76306772232056</v>
-      </c>
-      <c r="I14" s="68" t="n">
-        <v>29.29545402526855</v>
-      </c>
-      <c r="J14" s="68" t="n">
-        <v>45.10227203369141</v>
-      </c>
-      <c r="K14" s="68" t="n">
-        <v>50.6346583366394</v>
-      </c>
-      <c r="L14" s="68" t="n">
-        <v>60.90909004211426</v>
-      </c>
-      <c r="M14" s="68" t="n">
-        <v>76.71590805053711</v>
-      </c>
-      <c r="N14" s="68" t="n">
-        <v>76.71590805053711</v>
-      </c>
-      <c r="O14" s="68" t="n">
-        <v>0.7</v>
       </c>
       <c r="P14" s="68" t="n">
         <v>0.7</v>
@@ -7272,91 +7426,87 @@
         <v>1</v>
       </c>
       <c r="S14" s="68" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T14" s="68" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="U14" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_lrbs_use|All streams (pooled)</t>
+          <t>spring_phab_xbka|</t>
         </is>
       </c>
       <c r="B15" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-lrbs-use</t>
+          <t>spring-phab-xbka</t>
         </is>
       </c>
       <c r="C15" s="68" t="inlineStr">
         <is>
-          <t>Relative bed stability</t>
-        </is>
-      </c>
-      <c r="D15" s="68" t="inlineStr">
-        <is>
-          <t>All streams (pooled)</t>
-        </is>
-      </c>
+          <t>Bank angle</t>
+        </is>
+      </c>
+      <c r="D15" s="68" t="inlineStr"/>
       <c r="E15" s="68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="68" t="inlineStr">
         <is>
-          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate</t>
+          <t>34 least-disturbed streams of this ecoregion under the regional screen (agriculture at most 25 percent), carried forward from version 1</t>
         </is>
       </c>
       <c r="G15" s="68" t="n">
-        <v>-3.810347110033035</v>
+        <v>0</v>
       </c>
       <c r="H15" s="68" t="n">
-        <v>-2.740120500326157</v>
+        <v>23.76306772232056</v>
       </c>
       <c r="I15" s="68" t="n">
-        <v>-2.044473204016685</v>
+        <v>29.29545402526855</v>
       </c>
       <c r="J15" s="68" t="n">
-        <v>-1.669893890619278</v>
+        <v>45.10227203369141</v>
       </c>
       <c r="K15" s="68" t="n">
-        <v>-0.5996672809123993</v>
+        <v>50.6346583366394</v>
       </c>
       <c r="L15" s="68" t="n">
-        <v>-0.2250879675149918</v>
+        <v>60.90909004211426</v>
       </c>
       <c r="M15" s="68" t="n">
-        <v>0.4705593287944794</v>
+        <v>76.71590805053711</v>
       </c>
       <c r="N15" s="68" t="n">
-        <v>1.540785938501358</v>
+        <v>76.71590805053711</v>
       </c>
       <c r="O15" s="68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P15" s="68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q15" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T15" s="68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U15" s="68" t="n">
         <v>0</v>
-      </c>
-      <c r="P15" s="68" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q15" s="68" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R15" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" s="68" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U15" s="68" t="n">
-        <v>0.3</v>
       </c>
       <c r="V15" s="68" t="n">
         <v>0</v>
@@ -7365,7 +7515,7 @@
     <row r="16">
       <c r="A16" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_lrbs_use|Headwater (10 km2 and under)</t>
+          <t>spring_phab_lrbs_use|All streams (pooled)</t>
         </is>
       </c>
       <c r="B16" s="68" t="inlineStr">
@@ -7380,7 +7530,7 @@
       </c>
       <c r="D16" s="68" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="E16" s="68" t="n">
@@ -7388,32 +7538,32 @@
       </c>
       <c r="F16" s="68" t="inlineStr">
         <is>
-          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate</t>
+          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate, carried forward from version 1</t>
         </is>
       </c>
       <c r="G16" s="68" t="n">
-        <v>-4.181145370006561</v>
+        <v>-3.810347110033035</v>
       </c>
       <c r="H16" s="68" t="n">
-        <v>-2.935207813978195</v>
+        <v>-2.740120500326157</v>
       </c>
       <c r="I16" s="68" t="n">
-        <v>-2.125348402559757</v>
+        <v>-2.044473204016685</v>
       </c>
       <c r="J16" s="68" t="n">
-        <v>-1.689270257949829</v>
+        <v>-1.669893890619278</v>
       </c>
       <c r="K16" s="68" t="n">
-        <v>-0.443332701921463</v>
+        <v>-0.5996672809123993</v>
       </c>
       <c r="L16" s="68" t="n">
-        <v>-0.007254557311534904</v>
+        <v>-0.2250879675149918</v>
       </c>
       <c r="M16" s="68" t="n">
-        <v>0.8026048541069031</v>
+        <v>0.4705593287944794</v>
       </c>
       <c r="N16" s="68" t="n">
-        <v>2.048542410135269</v>
+        <v>1.540785938501358</v>
       </c>
       <c r="O16" s="68" t="n">
         <v>0</v>
@@ -7443,7 +7593,7 @@
     <row r="17">
       <c r="A17" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_lrbs_use|Small stream (10 to 100 km2)</t>
+          <t>spring_phab_lrbs_use|Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B17" s="68" t="inlineStr">
@@ -7458,7 +7608,7 @@
       </c>
       <c r="D17" s="68" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="E17" s="68" t="n">
@@ -7466,32 +7616,32 @@
       </c>
       <c r="F17" s="68" t="inlineStr">
         <is>
-          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate</t>
+          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate, carried forward from version 1</t>
         </is>
       </c>
       <c r="G17" s="68" t="n">
-        <v>-3.263704538345337</v>
+        <v>-4.181145370006561</v>
       </c>
       <c r="H17" s="68" t="n">
-        <v>-2.513432279229164</v>
+        <v>-2.935207813978195</v>
       </c>
       <c r="I17" s="68" t="n">
-        <v>-2.025755310803652</v>
+        <v>-2.125348402559757</v>
       </c>
       <c r="J17" s="68" t="n">
-        <v>-1.763160020112991</v>
+        <v>-1.689270257949829</v>
       </c>
       <c r="K17" s="68" t="n">
-        <v>-1.012887760996819</v>
+        <v>-0.443332701921463</v>
       </c>
       <c r="L17" s="68" t="n">
-        <v>-0.7502924703061581</v>
+        <v>-0.007254557311534904</v>
       </c>
       <c r="M17" s="68" t="n">
-        <v>-0.2626155018806458</v>
+        <v>0.8026048541069031</v>
       </c>
       <c r="N17" s="68" t="n">
-        <v>0.487656757235527</v>
+        <v>2.048542410135269</v>
       </c>
       <c r="O17" s="68" t="n">
         <v>0</v>
@@ -7521,7 +7671,7 @@
     <row r="18">
       <c r="A18" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_lrbs_use|Large stream (over 100 km2)</t>
+          <t>spring_phab_lrbs_use|Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="B18" s="68" t="inlineStr">
@@ -7536,7 +7686,7 @@
       </c>
       <c r="D18" s="68" t="inlineStr">
         <is>
-          <t>Large stream (over 100 km2)</t>
+          <t>Small stream (10 to 100 km2)</t>
         </is>
       </c>
       <c r="E18" s="68" t="n">
@@ -7544,32 +7694,32 @@
       </c>
       <c r="F18" s="68" t="inlineStr">
         <is>
-          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate</t>
+          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate, carried forward from version 1</t>
         </is>
       </c>
       <c r="G18" s="68" t="n">
-        <v>-3.468025326728821</v>
+        <v>-3.263704538345337</v>
       </c>
       <c r="H18" s="68" t="n">
-        <v>-2.517433404922485</v>
+        <v>-2.513432279229164</v>
       </c>
       <c r="I18" s="68" t="n">
-        <v>-1.899548655748367</v>
+        <v>-2.025755310803652</v>
       </c>
       <c r="J18" s="68" t="n">
-        <v>-1.56684148311615</v>
+        <v>-1.763160020112991</v>
       </c>
       <c r="K18" s="68" t="n">
-        <v>-0.6162495613098145</v>
+        <v>-1.012887760996819</v>
       </c>
       <c r="L18" s="68" t="n">
-        <v>-0.2835423886775971</v>
+        <v>-0.7502924703061581</v>
       </c>
       <c r="M18" s="68" t="n">
-        <v>0.334342360496521</v>
+        <v>-0.2626155018806458</v>
       </c>
       <c r="N18" s="68" t="n">
-        <v>1.284934282302856</v>
+        <v>0.487656757235527</v>
       </c>
       <c r="O18" s="68" t="n">
         <v>0</v>
@@ -7599,51 +7749,55 @@
     <row r="19">
       <c r="A19" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_lwdeqvolm100|</t>
+          <t>spring_phab_lrbs_use|Large stream (over 100 km2)</t>
         </is>
       </c>
       <c r="B19" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-lwdeqvolm100</t>
+          <t>spring-phab-lrbs-use</t>
         </is>
       </c>
       <c r="C19" s="68" t="inlineStr">
         <is>
-          <t>Large wood volume</t>
-        </is>
-      </c>
-      <c r="D19" s="68" t="inlineStr"/>
+          <t>Relative bed stability</t>
+        </is>
+      </c>
+      <c r="D19" s="68" t="inlineStr">
+        <is>
+          <t>Large stream (over 100 km2)</t>
+        </is>
+      </c>
       <c r="E19" s="68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" s="68" t="inlineStr">
         <is>
-          <t>14 least-disturbed stations of this ecoregion</t>
+          <t>84 least-disturbed stations borrowed from Level II ecoregion 8.3 (Southeastern Usa Plains) under the regional screen (agriculture at most 25 percent), transfer risk moderate, carried forward from version 1</t>
         </is>
       </c>
       <c r="G19" s="68" t="n">
-        <v>0</v>
+        <v>-3.468025326728821</v>
       </c>
       <c r="H19" s="68" t="n">
-        <v>0.1692187498722758</v>
+        <v>-2.517433404922485</v>
       </c>
       <c r="I19" s="68" t="n">
-        <v>0.3948437497019768</v>
+        <v>-1.899548655748367</v>
       </c>
       <c r="J19" s="68" t="n">
-        <v>3.514749944210052</v>
+        <v>-1.56684148311615</v>
       </c>
       <c r="K19" s="68" t="n">
-        <v>4.450721802562475</v>
+        <v>-0.6162495613098145</v>
       </c>
       <c r="L19" s="68" t="n">
-        <v>4.450721802562475</v>
+        <v>-0.2835423886775971</v>
       </c>
       <c r="M19" s="68" t="n">
-        <v>4.450721802562475</v>
+        <v>0.334342360496521</v>
       </c>
       <c r="N19" s="68" t="n">
-        <v>4.450721802562475</v>
+        <v>1.284934282302856</v>
       </c>
       <c r="O19" s="68" t="n">
         <v>0</v>
@@ -7661,29 +7815,29 @@
         <v>1</v>
       </c>
       <c r="T19" s="68" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="U19" s="68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="V19" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_xcdenmid|</t>
+          <t>spring_phab_lwdeqvolm100|</t>
         </is>
       </c>
       <c r="B20" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-xcdenmid</t>
+          <t>spring-phab-lwdeqvolm100</t>
         </is>
       </c>
       <c r="C20" s="68" t="inlineStr">
         <is>
-          <t>Canopy density, mid-channel</t>
+          <t>Large wood volume</t>
         </is>
       </c>
       <c r="D20" s="68" t="inlineStr"/>
@@ -7692,32 +7846,32 @@
       </c>
       <c r="F20" s="68" t="inlineStr">
         <is>
-          <t>16 least-disturbed stations of this ecoregion</t>
+          <t>14 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G20" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="68" t="n">
-        <v>35.29411860874721</v>
+        <v>0.1692187498722758</v>
       </c>
       <c r="I20" s="68" t="n">
-        <v>82.35294342041016</v>
+        <v>0.3948437497019768</v>
       </c>
       <c r="J20" s="68" t="n">
-        <v>99.29812812805176</v>
+        <v>3.514749944210052</v>
       </c>
       <c r="K20" s="68" t="n">
-        <v>100</v>
+        <v>4.450721802562475</v>
       </c>
       <c r="L20" s="68" t="n">
-        <v>100</v>
+        <v>4.450721802562475</v>
       </c>
       <c r="M20" s="68" t="n">
-        <v>100</v>
+        <v>4.450721802562475</v>
       </c>
       <c r="N20" s="68" t="n">
-        <v>100</v>
+        <v>4.450721802562475</v>
       </c>
       <c r="O20" s="68" t="n">
         <v>0</v>
@@ -7747,17 +7901,17 @@
     <row r="21">
       <c r="A21" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_xcmgw|</t>
+          <t>spring_phab_xcdenmid|</t>
         </is>
       </c>
       <c r="B21" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-xcmgw</t>
+          <t>spring-phab-xcdenmid</t>
         </is>
       </c>
       <c r="C21" s="68" t="inlineStr">
         <is>
-          <t>Riparian veg cover, woody</t>
+          <t>Canopy density, mid-channel</t>
         </is>
       </c>
       <c r="D21" s="68" t="inlineStr"/>
@@ -7766,32 +7920,32 @@
       </c>
       <c r="F21" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>16 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G21" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="68" t="n">
-        <v>0.4482954612800053</v>
+        <v>35.29411860874721</v>
       </c>
       <c r="I21" s="68" t="n">
-        <v>1.046022742986679</v>
+        <v>82.35294342041016</v>
       </c>
       <c r="J21" s="68" t="n">
-        <v>1.64318186044693</v>
+        <v>99.29812812805176</v>
       </c>
       <c r="K21" s="68" t="n">
-        <v>1.822329595685005</v>
+        <v>100</v>
       </c>
       <c r="L21" s="68" t="n">
-        <v>1.822329595685005</v>
+        <v>100</v>
       </c>
       <c r="M21" s="68" t="n">
-        <v>1.822329595685005</v>
+        <v>100</v>
       </c>
       <c r="N21" s="68" t="n">
-        <v>1.822329595685005</v>
+        <v>100</v>
       </c>
       <c r="O21" s="68" t="n">
         <v>0</v>
@@ -7821,17 +7975,17 @@
     <row r="22">
       <c r="A22" s="68" t="inlineStr">
         <is>
-          <t>spring_chem_ntl|</t>
+          <t>spring_phab_xcmgw|</t>
         </is>
       </c>
       <c r="B22" s="68" t="inlineStr">
         <is>
-          <t>spring-chem-ntl</t>
+          <t>spring-phab-xcmgw</t>
         </is>
       </c>
       <c r="C22" s="68" t="inlineStr">
         <is>
-          <t>Total nitrogen</t>
+          <t>Riparian veg cover, woody</t>
         </is>
       </c>
       <c r="D22" s="68" t="inlineStr"/>
@@ -7840,72 +7994,72 @@
       </c>
       <c r="F22" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G22" s="68" t="n">
-        <v>0.1551249980926514</v>
+        <v>0</v>
       </c>
       <c r="H22" s="68" t="n">
-        <v>0.2042500004172325</v>
+        <v>0.4482954612800053</v>
       </c>
       <c r="I22" s="68" t="n">
-        <v>0.3680000081658363</v>
+        <v>1.046022742986679</v>
       </c>
       <c r="J22" s="68" t="n">
-        <v>0.5863333518306414</v>
+        <v>1.64318186044693</v>
       </c>
       <c r="K22" s="68" t="n">
-        <v>0.7500833595792453</v>
+        <v>1.822329595685005</v>
       </c>
       <c r="L22" s="68" t="n">
-        <v>0.7500833595792453</v>
+        <v>1.822329595685005</v>
       </c>
       <c r="M22" s="68" t="n">
-        <v>0.7500833595792453</v>
+        <v>1.822329595685005</v>
       </c>
       <c r="N22" s="68" t="n">
-        <v>0.7500833595792453</v>
+        <v>1.822329595685005</v>
       </c>
       <c r="O22" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q22" s="68" t="n">
         <v>0.7</v>
       </c>
       <c r="R22" s="68" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="S22" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="68" t="inlineStr">
         <is>
-          <t>spring_chem_ptl|</t>
+          <t>spring_chem_ntl|</t>
         </is>
       </c>
       <c r="B23" s="68" t="inlineStr">
         <is>
-          <t>spring-chem-ptl</t>
+          <t>spring-chem-ntl</t>
         </is>
       </c>
       <c r="C23" s="68" t="inlineStr">
         <is>
-          <t>Total phosphorus</t>
+          <t>Total nitrogen</t>
         </is>
       </c>
       <c r="D23" s="68" t="inlineStr"/>
@@ -7914,32 +8068,32 @@
       </c>
       <c r="F23" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G23" s="68" t="n">
-        <v>11.21087503433228</v>
+        <v>0.1551249980926514</v>
       </c>
       <c r="H23" s="68" t="n">
-        <v>22.42224979400635</v>
+        <v>0.2042500004172325</v>
       </c>
       <c r="I23" s="68" t="n">
-        <v>59.79349899291992</v>
+        <v>0.3680000081658363</v>
       </c>
       <c r="J23" s="68" t="n">
-        <v>109.621831258138</v>
+        <v>0.5863333518306414</v>
       </c>
       <c r="K23" s="68" t="n">
-        <v>146.9930804570516</v>
+        <v>0.7500833595792453</v>
       </c>
       <c r="L23" s="68" t="n">
-        <v>146.9930804570516</v>
+        <v>0.7500833595792453</v>
       </c>
       <c r="M23" s="68" t="n">
-        <v>146.9930804570516</v>
+        <v>0.7500833595792453</v>
       </c>
       <c r="N23" s="68" t="n">
-        <v>146.9930804570516</v>
+        <v>0.7500833595792453</v>
       </c>
       <c r="O23" s="68" t="n">
         <v>1</v>
@@ -7969,72 +8123,72 @@
     <row r="24">
       <c r="A24" s="68" t="inlineStr">
         <is>
-          <t>spring_chem_ph|</t>
+          <t>spring_chem_ptl|</t>
         </is>
       </c>
       <c r="B24" s="68" t="inlineStr">
         <is>
-          <t>spring-chem-ph</t>
+          <t>spring-chem-ptl</t>
         </is>
       </c>
       <c r="C24" s="68" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Total phosphorus</t>
         </is>
       </c>
       <c r="D24" s="68" t="inlineStr"/>
       <c r="E24" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F24" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G24" s="68" t="n">
-        <v>5.404999852180481</v>
+        <v>11.21087503433228</v>
       </c>
       <c r="H24" s="68" t="n">
-        <v>6.129999876022339</v>
+        <v>22.42224979400635</v>
       </c>
       <c r="I24" s="68" t="n">
-        <v>6.601249891519546</v>
+        <v>59.79349899291992</v>
       </c>
       <c r="J24" s="68" t="n">
-        <v>6.854999899864197</v>
+        <v>109.621831258138</v>
       </c>
       <c r="K24" s="68" t="n">
-        <v>7.579999923706055</v>
+        <v>146.9930804570516</v>
       </c>
       <c r="L24" s="68" t="n">
-        <v>7.833749932050705</v>
+        <v>146.9930804570516</v>
       </c>
       <c r="M24" s="68" t="n">
-        <v>8.304999947547913</v>
+        <v>146.9930804570516</v>
       </c>
       <c r="N24" s="68" t="n">
-        <v>9.029999971389771</v>
+        <v>146.9930804570516</v>
       </c>
       <c r="O24" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="68" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q24" s="68" t="n">
         <v>0.7</v>
       </c>
       <c r="R24" s="68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S24" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" s="68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="U24" s="68" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="V24" s="68" t="n">
         <v>0</v>
@@ -8043,72 +8197,72 @@
     <row r="25">
       <c r="A25" s="68" t="inlineStr">
         <is>
-          <t>spring_chem_turb|</t>
+          <t>spring_chem_ph|</t>
         </is>
       </c>
       <c r="B25" s="68" t="inlineStr">
         <is>
-          <t>spring-chem-turb</t>
+          <t>spring-chem-ph</t>
         </is>
       </c>
       <c r="C25" s="68" t="inlineStr">
         <is>
-          <t>Turbidity</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="D25" s="68" t="inlineStr"/>
       <c r="E25" s="68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F25" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G25" s="68" t="n">
-        <v>3.253250157833099</v>
+        <v>5.404999852180481</v>
       </c>
       <c r="H25" s="68" t="n">
-        <v>5.96750009059906</v>
+        <v>6.129999876022339</v>
       </c>
       <c r="I25" s="68" t="n">
-        <v>15.0149998664856</v>
+        <v>6.601249891519546</v>
       </c>
       <c r="J25" s="68" t="n">
-        <v>27.07833290100098</v>
+        <v>6.854999899864197</v>
       </c>
       <c r="K25" s="68" t="n">
-        <v>36.12583267688751</v>
+        <v>7.579999923706055</v>
       </c>
       <c r="L25" s="68" t="n">
-        <v>36.12583267688751</v>
+        <v>7.833749932050705</v>
       </c>
       <c r="M25" s="68" t="n">
-        <v>36.12583267688751</v>
+        <v>8.304999947547913</v>
       </c>
       <c r="N25" s="68" t="n">
-        <v>36.12583267688751</v>
+        <v>9.029999971389771</v>
       </c>
       <c r="O25" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q25" s="68" t="n">
         <v>0.7</v>
       </c>
       <c r="R25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U25" s="68" t="n">
         <v>0.3</v>
-      </c>
-      <c r="S25" s="68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="68" t="n">
-        <v>0</v>
       </c>
       <c r="V25" s="68" t="n">
         <v>0</v>
@@ -8117,17 +8271,17 @@
     <row r="26">
       <c r="A26" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_pct_fast|</t>
+          <t>spring_chem_turb|</t>
         </is>
       </c>
       <c r="B26" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-pct-fast</t>
+          <t>spring-chem-turb</t>
         </is>
       </c>
       <c r="C26" s="68" t="inlineStr">
         <is>
-          <t>Fast-water / riffle habitat</t>
+          <t>Turbidity</t>
         </is>
       </c>
       <c r="D26" s="68" t="inlineStr"/>
@@ -8136,72 +8290,72 @@
       </c>
       <c r="F26" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G26" s="68" t="n">
-        <v>0</v>
+        <v>3.253250157833099</v>
       </c>
       <c r="H26" s="68" t="n">
-        <v>0.5714285692998341</v>
+        <v>5.96750009059906</v>
       </c>
       <c r="I26" s="68" t="n">
-        <v>1.33333332836628</v>
+        <v>15.0149998664856</v>
       </c>
       <c r="J26" s="68" t="n">
-        <v>14.74999976158142</v>
+        <v>27.07833290100098</v>
       </c>
       <c r="K26" s="68" t="n">
-        <v>18.77499969154596</v>
+        <v>36.12583267688751</v>
       </c>
       <c r="L26" s="68" t="n">
-        <v>18.77499969154596</v>
+        <v>36.12583267688751</v>
       </c>
       <c r="M26" s="68" t="n">
-        <v>18.77499969154596</v>
+        <v>36.12583267688751</v>
       </c>
       <c r="N26" s="68" t="n">
-        <v>18.77499969154596</v>
+        <v>36.12583267688751</v>
       </c>
       <c r="O26" s="68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="68" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="68" t="n">
         <v>0.7</v>
       </c>
       <c r="R26" s="68" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="S26" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="68" t="inlineStr">
         <is>
-          <t>spring_phab_xfc_nat|</t>
+          <t>spring_phab_pct_fast|</t>
         </is>
       </c>
       <c r="B27" s="68" t="inlineStr">
         <is>
-          <t>spring-phab-xfc-nat</t>
+          <t>spring-phab-pct-fast</t>
         </is>
       </c>
       <c r="C27" s="68" t="inlineStr">
         <is>
-          <t>Natural fish cover</t>
+          <t>Fast-water / riffle habitat</t>
         </is>
       </c>
       <c r="D27" s="68" t="inlineStr"/>
@@ -8210,32 +8364,32 @@
       </c>
       <c r="F27" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G27" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="68" t="n">
-        <v>0.09642857206719262</v>
+        <v>0.5714285692998341</v>
       </c>
       <c r="I27" s="68" t="n">
-        <v>0.2250000014901161</v>
+        <v>1.33333332836628</v>
       </c>
       <c r="J27" s="68" t="n">
-        <v>0.9397727400064468</v>
+        <v>14.74999976158142</v>
       </c>
       <c r="K27" s="68" t="n">
-        <v>1.154204561561346</v>
+        <v>18.77499969154596</v>
       </c>
       <c r="L27" s="68" t="n">
-        <v>1.154204561561346</v>
+        <v>18.77499969154596</v>
       </c>
       <c r="M27" s="68" t="n">
-        <v>1.154204561561346</v>
+        <v>18.77499969154596</v>
       </c>
       <c r="N27" s="68" t="n">
-        <v>1.154204561561346</v>
+        <v>18.77499969154596</v>
       </c>
       <c r="O27" s="68" t="n">
         <v>0</v>
@@ -8265,17 +8419,17 @@
     <row r="28">
       <c r="A28" s="68" t="inlineStr">
         <is>
-          <t>spring_bent_totlntax|</t>
+          <t>spring_phab_xfc_nat|</t>
         </is>
       </c>
       <c r="B28" s="68" t="inlineStr">
         <is>
-          <t>spring-bent-totlntax</t>
+          <t>spring-phab-xfc-nat</t>
         </is>
       </c>
       <c r="C28" s="68" t="inlineStr">
         <is>
-          <t>Benthic total taxa richness</t>
+          <t>Natural fish cover</t>
         </is>
       </c>
       <c r="D28" s="68" t="inlineStr"/>
@@ -8284,32 +8438,32 @@
       </c>
       <c r="F28" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G28" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="68" t="n">
-        <v>6.964285714285714</v>
+        <v>0.09642857206719262</v>
       </c>
       <c r="I28" s="68" t="n">
-        <v>16.25</v>
+        <v>0.2250000014901161</v>
       </c>
       <c r="J28" s="68" t="n">
-        <v>42.75</v>
+        <v>0.9397727400064468</v>
       </c>
       <c r="K28" s="68" t="n">
-        <v>50.7</v>
+        <v>1.154204561561346</v>
       </c>
       <c r="L28" s="68" t="n">
-        <v>50.7</v>
+        <v>1.154204561561346</v>
       </c>
       <c r="M28" s="68" t="n">
-        <v>50.7</v>
+        <v>1.154204561561346</v>
       </c>
       <c r="N28" s="68" t="n">
-        <v>50.7</v>
+        <v>1.154204561561346</v>
       </c>
       <c r="O28" s="68" t="n">
         <v>0</v>
@@ -8339,17 +8493,17 @@
     <row r="29">
       <c r="A29" s="68" t="inlineStr">
         <is>
-          <t>spring_fish_nat_totlntax|</t>
+          <t>spring_bent_totlntax|</t>
         </is>
       </c>
       <c r="B29" s="68" t="inlineStr">
         <is>
-          <t>spring-fish-nat-totlntax</t>
+          <t>spring-bent-totlntax</t>
         </is>
       </c>
       <c r="C29" s="68" t="inlineStr">
         <is>
-          <t>Native fish taxa richness</t>
+          <t>Benthic total taxa richness</t>
         </is>
       </c>
       <c r="D29" s="68" t="inlineStr"/>
@@ -8358,32 +8512,32 @@
       </c>
       <c r="F29" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G29" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="68" t="n">
-        <v>2.357142857142857</v>
+        <v>6.964285714285714</v>
       </c>
       <c r="I29" s="68" t="n">
-        <v>5.5</v>
+        <v>16.25</v>
       </c>
       <c r="J29" s="68" t="n">
-        <v>15.75</v>
+        <v>42.75</v>
       </c>
       <c r="K29" s="68" t="n">
-        <v>18.825</v>
+        <v>50.7</v>
       </c>
       <c r="L29" s="68" t="n">
-        <v>18.825</v>
+        <v>50.7</v>
       </c>
       <c r="M29" s="68" t="n">
-        <v>18.825</v>
+        <v>50.7</v>
       </c>
       <c r="N29" s="68" t="n">
-        <v>18.825</v>
+        <v>50.7</v>
       </c>
       <c r="O29" s="68" t="n">
         <v>0</v>
@@ -8413,17 +8567,17 @@
     <row r="30">
       <c r="A30" s="68" t="inlineStr">
         <is>
-          <t>spring_bent_ept_ntax|</t>
+          <t>spring_fish_nat_totlntax|</t>
         </is>
       </c>
       <c r="B30" s="68" t="inlineStr">
         <is>
-          <t>spring-bent-ept-ntax</t>
+          <t>spring-fish-nat-totlntax</t>
         </is>
       </c>
       <c r="C30" s="68" t="inlineStr">
         <is>
-          <t>EPT taxa richness</t>
+          <t>Native fish taxa richness</t>
         </is>
       </c>
       <c r="D30" s="68" t="inlineStr"/>
@@ -8432,32 +8586,32 @@
       </c>
       <c r="F30" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G30" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="68" t="n">
-        <v>0.5357142857142857</v>
+        <v>2.357142857142857</v>
       </c>
       <c r="I30" s="68" t="n">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="J30" s="68" t="n">
-        <v>9</v>
+        <v>15.75</v>
       </c>
       <c r="K30" s="68" t="n">
-        <v>11.325</v>
+        <v>18.825</v>
       </c>
       <c r="L30" s="68" t="n">
-        <v>11.325</v>
+        <v>18.825</v>
       </c>
       <c r="M30" s="68" t="n">
-        <v>11.325</v>
+        <v>18.825</v>
       </c>
       <c r="N30" s="68" t="n">
-        <v>11.325</v>
+        <v>18.825</v>
       </c>
       <c r="O30" s="68" t="n">
         <v>0</v>
@@ -8487,17 +8641,17 @@
     <row r="31">
       <c r="A31" s="68" t="inlineStr">
         <is>
-          <t>spring_bent_hprime|</t>
+          <t>spring_bent_ept_ntax|</t>
         </is>
       </c>
       <c r="B31" s="68" t="inlineStr">
         <is>
-          <t>spring-bent-hprime</t>
+          <t>spring-bent-ept-ntax</t>
         </is>
       </c>
       <c r="C31" s="68" t="inlineStr">
         <is>
-          <t>Shannon diversity (H')</t>
+          <t>EPT taxa richness</t>
         </is>
       </c>
       <c r="D31" s="68" t="inlineStr"/>
@@ -8506,32 +8660,32 @@
       </c>
       <c r="F31" s="68" t="inlineStr">
         <is>
-          <t>18 least-disturbed stations of this ecoregion</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G31" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="68" t="n">
-        <v>0.9910714030265808</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="I31" s="68" t="n">
-        <v>2.312499940395355</v>
+        <v>1.25</v>
       </c>
       <c r="J31" s="68" t="n">
-        <v>3.132500052452087</v>
+        <v>9</v>
       </c>
       <c r="K31" s="68" t="n">
-        <v>3.378500086069107</v>
+        <v>11.325</v>
       </c>
       <c r="L31" s="68" t="n">
-        <v>3.378500086069107</v>
+        <v>11.325</v>
       </c>
       <c r="M31" s="68" t="n">
-        <v>3.378500086069107</v>
+        <v>11.325</v>
       </c>
       <c r="N31" s="68" t="n">
-        <v>3.378500086069107</v>
+        <v>11.325</v>
       </c>
       <c r="O31" s="68" t="n">
         <v>0</v>
@@ -8561,100 +8715,162 @@
     <row r="32">
       <c r="A32" s="68" t="inlineStr">
         <is>
-          <t>spring_nid_dams_1mi|</t>
+          <t>spring_bent_hprime|</t>
         </is>
       </c>
       <c r="B32" s="68" t="inlineStr">
         <is>
-          <t>spring-nid-dams-1mi</t>
+          <t>spring-bent-hprime</t>
         </is>
       </c>
       <c r="C32" s="68" t="inlineStr">
         <is>
-          <t>Mapped dams within one mile</t>
+          <t>Shannon diversity (H')</t>
         </is>
       </c>
       <c r="D32" s="68" t="inlineStr"/>
       <c r="E32" s="68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="68" t="inlineStr">
         <is>
-          <t>Fixed criteria, the same in every region</t>
+          <t>18 least-disturbed stations of this ecoregion, carried forward from version 1</t>
         </is>
       </c>
       <c r="G32" s="68" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="68" t="n">
-        <v>1</v>
+        <v>0.9910714030265808</v>
       </c>
       <c r="I32" s="68" t="n">
+        <v>2.312499940395355</v>
+      </c>
+      <c r="J32" s="68" t="n">
+        <v>3.132500052452087</v>
+      </c>
+      <c r="K32" s="68" t="n">
+        <v>3.378500086069107</v>
+      </c>
+      <c r="L32" s="68" t="n">
+        <v>3.378500086069107</v>
+      </c>
+      <c r="M32" s="68" t="n">
+        <v>3.378500086069107</v>
+      </c>
+      <c r="N32" s="68" t="n">
+        <v>3.378500086069107</v>
+      </c>
+      <c r="O32" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="68" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q32" s="68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R32" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="68" t="inlineStr">
+        <is>
+          <t>spring_nid_dams_1mi|</t>
+        </is>
+      </c>
+      <c r="B33" s="68" t="inlineStr">
+        <is>
+          <t>spring-nid-dams-1mi</t>
+        </is>
+      </c>
+      <c r="C33" s="68" t="inlineStr">
+        <is>
+          <t>Mapped dams within one mile</t>
+        </is>
+      </c>
+      <c r="D33" s="68" t="inlineStr"/>
+      <c r="E33" s="68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="68" t="inlineStr">
+        <is>
+          <t>Fixed criteria, the same in every region</t>
+        </is>
+      </c>
+      <c r="G33" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="68" t="n">
+      <c r="J33" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="68" t="n">
+      <c r="K33" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="68" t="n">
+      <c r="L33" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="M32" s="68" t="n">
+      <c r="M33" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="68" t="n">
+      <c r="N33" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="O32" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="68" t="n">
+      <c r="O33" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="68" t="n">
         <v>0.545</v>
       </c>
-      <c r="Q32" s="68" t="n">
+      <c r="Q33" s="68" t="n">
         <v>0.195</v>
       </c>
-      <c r="R32" s="68" t="n">
+      <c r="R33" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="68" t="n">
+      <c r="S33" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="T32" s="68" t="n">
+      <c r="T33" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="68" t="n">
+      <c r="U33" s="68" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="68" t="n">
+      <c r="V33" s="68" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="57" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="57" t="inlineStr">
         <is>
           <t>Curve sets by metric</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="68" t="inlineStr">
-        <is>
-          <t>All streams (pooled)</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Relative bed stability</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="68" t="inlineStr">
         <is>
-          <t>Headwater (10 km2 and under)</t>
+          <t>All streams (pooled)</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -8666,7 +8882,7 @@
     <row r="38">
       <c r="A38" s="68" t="inlineStr">
         <is>
-          <t>Small stream (10 to 100 km2)</t>
+          <t>Headwater (10 km2 and under)</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -8678,38 +8894,50 @@
     <row r="39">
       <c r="A39" s="68" t="inlineStr">
         <is>
+          <t>Small stream (10 to 100 km2)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Relative bed stability</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="68" t="inlineStr">
+        <is>
           <t>Large stream (over 100 km2)</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Relative bed stability</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="57" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="57" t="inlineStr">
         <is>
           <t>Condition classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
+          <t>Metric index: at or below 0.39 Non-Functioning, at or below 0.69 Functioning At-Risk, above Functioning.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
+        <is>
+          <t>Function score (0 to 15): at or below 5 Non-Functioning, at or below 10 Functioning At-Risk, above Functioning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Outcome weights: a direct contribution counts 1, an indirect one 0.1.</t>
         </is>
@@ -8784,7 +9012,7 @@
         </is>
       </c>
       <c r="B6" s="68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -8803,7 +9031,7 @@
       </c>
       <c r="B8" s="68" t="inlineStr">
         <is>
-          <t>sha256:8abb4be427ffede5aa948f81b33bbfafb5ecd83776962e58938ad3f253b4bdcd</t>
+          <t>sha256:fe2aca83722659416d0eccddf8e01ac668272363e995ca238259f7edf1971856</t>
         </is>
       </c>
     </row>
@@ -8874,7 +9102,7 @@
         </is>
       </c>
       <c r="B14" s="68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -8884,7 +9112,7 @@
         </is>
       </c>
       <c r="B15" s="68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -8895,7 +9123,7 @@
       </c>
       <c r="B16" s="68" t="inlineStr">
         <is>
-          <t>This assessment covers 19 of 20 STAF functions (1 documented exclusions).</t>
+          <t>This assessment covers 20 of 20 STAF functions.</t>
         </is>
       </c>
     </row>
@@ -8947,7 +9175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9013,7 +9241,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reach inflow</t>
+          <t>Surface water storage</t>
         </is>
       </c>
       <c r="B4">
@@ -9036,7 +9264,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Streamflow regime</t>
+          <t>Reach inflow</t>
         </is>
       </c>
       <c r="B5">
@@ -9059,7 +9287,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Low flow and baseflow dynamics</t>
+          <t>Streamflow regime</t>
         </is>
       </c>
       <c r="B6">
@@ -9082,7 +9310,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High flow dynamics</t>
+          <t>Low flow and baseflow dynamics</t>
         </is>
       </c>
       <c r="B7">
@@ -9105,7 +9333,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Floodplain connectivity</t>
+          <t>High flow dynamics</t>
         </is>
       </c>
       <c r="B8">
@@ -9128,7 +9356,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hyporheic connectivity</t>
+          <t>Floodplain connectivity</t>
         </is>
       </c>
       <c r="B9">
@@ -9151,7 +9379,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Channel evolution</t>
+          <t>Hyporheic connectivity</t>
         </is>
       </c>
       <c r="B10">
@@ -9174,7 +9402,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Channel and floodplain dynamics</t>
+          <t>Channel evolution</t>
         </is>
       </c>
       <c r="B11">
@@ -9197,7 +9425,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sediment continuity</t>
+          <t>Channel and floodplain dynamics</t>
         </is>
       </c>
       <c r="B12">
@@ -9220,7 +9448,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bed composition and bedform dynamics</t>
+          <t>Sediment continuity</t>
         </is>
       </c>
       <c r="B13">
@@ -9243,7 +9471,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Light &amp; thermal regime</t>
+          <t>Bed composition and bedform dynamics</t>
         </is>
       </c>
       <c r="B14">
@@ -9266,7 +9494,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Carbon processing</t>
+          <t>Light &amp; thermal regime</t>
         </is>
       </c>
       <c r="B15">
@@ -9289,7 +9517,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nutrient cycling</t>
+          <t>Carbon processing</t>
         </is>
       </c>
       <c r="B16">
@@ -9312,7 +9540,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Water &amp; soil quality</t>
+          <t>Nutrient cycling</t>
         </is>
       </c>
       <c r="B17">
@@ -9335,7 +9563,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Habitat provision</t>
+          <t>Water &amp; soil quality</t>
         </is>
       </c>
       <c r="B18">
@@ -9358,7 +9586,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Population support</t>
+          <t>Habitat provision</t>
         </is>
       </c>
       <c r="B19">
@@ -9381,7 +9609,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Community dynamics</t>
+          <t>Population support</t>
         </is>
       </c>
       <c r="B20">
@@ -9404,7 +9632,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Watershed connectivity</t>
+          <t>Community dynamics</t>
         </is>
       </c>
       <c r="B21">
@@ -9424,60 +9652,60 @@
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="57" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Watershed connectivity</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>IF('Results'!$B$23="","",'Results'!$B$23)</f>
+        <v/>
+      </c>
+      <c r="C22" s="71">
+        <f>IF(ISNUMBER('ChartData'!$B$22),IF('ChartData'!$B$22&lt;=5,'ChartData'!$B$22,NA()),NA())</f>
+        <v/>
+      </c>
+      <c r="D22" s="71">
+        <f>IF(ISNUMBER('ChartData'!$B$22),IF(AND('ChartData'!$B$22&gt;5,'ChartData'!$B$22&lt;=10),'ChartData'!$B$22,NA()),NA())</f>
+        <v/>
+      </c>
+      <c r="E22" s="71">
+        <f>IF(ISNUMBER('ChartData'!$B$22),IF('ChartData'!$B$22&gt;10,'ChartData'!$B$22,NA()),NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="57" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="B23" s="57" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C23" s="57" t="inlineStr">
+      <c r="C24" s="57" t="inlineStr">
         <is>
           <t>Non-Functioning (0.00-0.39)</t>
         </is>
       </c>
-      <c r="D23" s="57" t="inlineStr">
+      <c r="D24" s="57" t="inlineStr">
         <is>
           <t>Functioning At-Risk (0.40-0.69)</t>
         </is>
       </c>
-      <c r="E23" s="57" t="inlineStr">
+      <c r="E24" s="57" t="inlineStr">
         <is>
           <t>Functioning (0.70-1.00)</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Physical</t>
-        </is>
-      </c>
-      <c r="B24">
-        <f>'Results'!$B$25</f>
-        <v/>
-      </c>
-      <c r="C24" s="72">
-        <f>IF('ChartData'!$B$24&lt;=0.39,'ChartData'!$B$24,NA())</f>
-        <v/>
-      </c>
-      <c r="D24" s="72">
-        <f>IF(AND('ChartData'!$B$24&gt;0.39,'ChartData'!$B$24&lt;=0.69),'ChartData'!$B$24,NA())</f>
-        <v/>
-      </c>
-      <c r="E24" s="72">
-        <f>IF('ChartData'!$B$24&gt;0.69,'ChartData'!$B$24,NA())</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Physical</t>
         </is>
       </c>
       <c r="B25">
@@ -9500,7 +9728,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="B26">
@@ -9517,6 +9745,29 @@
       </c>
       <c r="E26" s="72">
         <f>IF('ChartData'!$B$26&gt;0.69,'ChartData'!$B$26,NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Biological</t>
+        </is>
+      </c>
+      <c r="B27">
+        <f>'Results'!$B$28</f>
+        <v/>
+      </c>
+      <c r="C27" s="72">
+        <f>IF('ChartData'!$B$27&lt;=0.39,'ChartData'!$B$27,NA())</f>
+        <v/>
+      </c>
+      <c r="D27" s="72">
+        <f>IF(AND('ChartData'!$B$27&gt;0.39,'ChartData'!$B$27&lt;=0.69),'ChartData'!$B$27,NA())</f>
+        <v/>
+      </c>
+      <c r="E27" s="72">
+        <f>IF('ChartData'!$B$27&gt;0.69,'ChartData'!$B$27,NA())</f>
         <v/>
       </c>
     </row>
